--- a/finance/_refresh_yassir.xlsx
+++ b/finance/_refresh_yassir.xlsx
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Cap on revenue sailings/day — MID headline duty cycle; thin=12 / full=18 bookends in _utilization_scenarios (Jaideep 2026-06-21).</t>
+          <t>Cap on revenue sailings/day — 15 across thin/mid/full scenarios (Jaideep 2026-06-21).</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
         <v>0.7</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>

--- a/finance/_refresh_yassir.xlsx
+++ b/finance/_refresh_yassir.xlsx
@@ -27,23 +27,23 @@
     <definedName name="dwell_min">'Assumptions'!$B$18</definedName>
     <definedName name="max_tpd">'Assumptions'!$B$19</definedName>
     <definedName name="crew_factor">'Assumptions'!$B$20</definedName>
-    <definedName name="ins_pct">'Assumptions'!$B$21</definedName>
-    <definedName name="charge_berth">'Assumptions'!$B$22</definedName>
-    <definedName name="mech_uptime">'Assumptions'!$B$23</definedName>
-    <definedName name="capture">'Assumptions'!$B$24</definedName>
-    <definedName name="capture_captive">'Assumptions'!$B$25</definedName>
-    <definedName name="discount">'Assumptions'!$B$26</definedName>
-    <definedName name="diesel_co2pg">'Assumptions'!$B$27</definedName>
-    <definedName name="load_thin">'Assumptions'!$B$31</definedName>
-    <definedName name="revleg_thin">'Assumptions'!$C$31</definedName>
-    <definedName name="load_mid">'Assumptions'!$B$32</definedName>
-    <definedName name="revleg_mid">'Assumptions'!$C$32</definedName>
-    <definedName name="load_full">'Assumptions'!$B$33</definedName>
-    <definedName name="revleg_full">'Assumptions'!$C$33</definedName>
-    <definedName name="band_tbl">'Assumptions'!$A$31:$C$33</definedName>
-    <definedName name="scenario">'Assumptions'!$B$35</definedName>
-    <definedName name="load_sel">'Assumptions'!$B$36</definedName>
-    <definedName name="revleg_sel">'Assumptions'!$B$37</definedName>
+    <definedName name="mech_uptime">'Assumptions'!$B$21</definedName>
+    <definedName name="capture">'Assumptions'!$B$22</definedName>
+    <definedName name="capture_captive">'Assumptions'!$B$23</definedName>
+    <definedName name="discount">'Assumptions'!$B$24</definedName>
+    <definedName name="diesel_co2pg">'Assumptions'!$B$25</definedName>
+    <definedName name="ins_pct">'Assumptions'!$B$29</definedName>
+    <definedName name="charge_berth">'Assumptions'!$B$30</definedName>
+    <definedName name="load_thin">'Assumptions'!$B$34</definedName>
+    <definedName name="revleg_thin">'Assumptions'!$C$34</definedName>
+    <definedName name="load_mid">'Assumptions'!$B$35</definedName>
+    <definedName name="revleg_mid">'Assumptions'!$C$35</definedName>
+    <definedName name="load_full">'Assumptions'!$B$36</definedName>
+    <definedName name="revleg_full">'Assumptions'!$C$36</definedName>
+    <definedName name="band_tbl">'Assumptions'!$A$34:$C$36</definedName>
+    <definedName name="scenario">'Assumptions'!$B$38</definedName>
+    <definedName name="load_sel">'Assumptions'!$B$39</definedName>
+    <definedName name="revleg_sel">'Assumptions'!$B$40</definedName>
     <definedName name="country_opex">'Country opex'!$A$4:$G$6</definedName>
     <definedName name="som_floor_fleet">'Corridor economics'!$D$27</definedName>
     <definedName name="som_floor_rev">'Corridor economics'!$E$27</definedName>
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B27"/>
+  <dimension ref="B2:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -780,84 +780,143 @@
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>EBITDA  = REVENUE − OPEX   (energy + captain + marina/overhead + maintenance)</t>
+          <t>EBITDA  = REVENUE − OPEX</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    OPEX = energy + crew + berth/port admin + maintenance + vessel insurance + fast-charge berth</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>PAYBACK = vessel CAPEX ÷ EBITDA</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="2" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>From demand pool to fleet &amp; market size</t>
-        </is>
-      </c>
+      <c r="B17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Navier serviceable rides/yr = corridor demand pool × capture rate (10% on contested corridors; ~90% on captive sole-operator transfer legs — see the per-row Capture % column)</t>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>OPEX lines (per boat, per year — no double-counting)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Vessels supported = FLOOR(Navier rides/yr ÷ pax/yr per boat);  Market rev = vessels × rev/boat. The 'Market sizing' tab rolls these up into the SOM → SAM → TAM ladder.</t>
+          <t>Energy — variable propulsion cost: kWh on revenue sailings × local $/kWh (Country opex tab). Excludes utility demand charges.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Crew — fully-loaded captain + relief: local captain wage × crew FTE factor (Country opex + Assumptions).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>The scenario toggle (what we flex)</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Berth &amp; port admin — fixed annual berth, port fees, and local marine admin (Country opex tab). Excludes vessel H&amp;M+P&amp;I and fast-charge infrastructure.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>'Corridor economics' has a SCENARIO cell = THIN / MID / FULL. It flexes two levers: load factor (how full the boat is) and revenue-leg factor (how many legs earn full fare). MID is the headline. Change that one cell and the whole model recomputes. The right-hand Payback THIN/MID/FULL columns always show all three at once.</t>
+          <t>Maintenance — vessel annual maintenance reserve (Assumptions tab).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Vessel insurance — commercial H&amp;M + P&amp;I as % of regional CAPEX (Assumptions % × Country opex CAPEX column).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Fast-charge berth — dedicated fast-charge berth slot + utility demand charges (Assumptions default; overridable per market). Separate from per-kWh energy and berth/port admin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>From demand pool to fleet &amp; market size</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Navier serviceable rides/yr = corridor demand pool × capture rate (10% on contested corridors; ~90% on captive sole-operator transfer legs — see the per-row Capture % column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Vessels supported = FLOOR(Navier rides/yr ÷ pax/yr per boat);  Market rev = vessels × rev/boat. The 'Market sizing' tab rolls these up into the SOM → SAM → TAM ladder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>The scenario toggle (what we flex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>'Corridor economics' has a SCENARIO cell = THIN / MID / FULL. It flexes load factor (occupancy) and revenue-leg factor (share of legs that earn full fare). Max trips/day is fixed across all three bands (see Assumptions). MID is the headline. Change SCENARIO and the whole model recomputes. Payback THIN/MID/FULL columns always show all three at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Colour &amp; provenance legend</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="6" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">   Yellow = INPUTS you can change (fare, distance, demand, weather).</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="7" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   Green  = COMPUTED by formula.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="2" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   Every fare &amp; demand figure carries a Source tier (T1 official → T5 modeled) + Confidence (high/med/low). Null beats a wrong number: no published pool → blank, not a guess.</t>
         </is>
@@ -874,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1363,11 +1422,11 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Insurance (% of capex/yr)</t>
+          <t>Mechanical uptime</t>
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>0.025</v>
+        <v>0.75</v>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
@@ -1376,7 +1435,7 @@
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -1386,29 +1445,25 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>H&amp;M + P&amp;I for a commercial passenger vessel ~2.5%/yr of capex; scales with regional capex overrides (Jaideep 2026-06-19).</t>
+          <t>Blade luxury aviation ~75-80% reliability uptime</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Charging &amp; berth (additional to marina+energy)</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n">
-        <v>18000</v>
+          <t>Navier capture rate</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>0.1</v>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>USD/yr</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
+          <t>frac</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr"/>
       <c r="E22" s="13" t="inlineStr">
         <is>
           <t>med</t>
@@ -1416,29 +1471,25 @@
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Dedicated fast-charge berth + demand charges, ADDITIONAL to marina overhead and energy (Jaideep 2026-06-19). L3-overridable.</t>
+          <t>Navier wins ~10% of a CONTESTED corridor demand pool (locked). Captive sole-operator transfer legs (captive:true / luxury_charter / hospitality archetypes) carry the captive rate instead — see per-row Capture %.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Mechanical uptime</t>
+          <t>Captive capture rate (A′ corridors)</t>
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
+      <c r="D23" s="13" t="inlineStr"/>
       <c r="E23" s="13" t="inlineStr">
         <is>
           <t>med</t>
@@ -1446,255 +1497,303 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Blade luxury aviation ~75-80% reliability uptime</t>
+          <t>Sole-operator water-access-only transfer legs (captive:true or luxury_charter/hospitality archetype): Navier IS the transfer fleet — capture ~90%. Applied per-row in the Capture % column.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Navier capture rate</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="n">
-        <v>0.1</v>
+          <t>Discount factor (vs comparable fare)</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr"/>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Navier wins ~10% of a CONTESTED corridor demand pool (locked). Captive sole-operator transfer legs (captive:true / luxury_charter / hospitality archetypes) carry the captive rate instead — see per-row Capture %.</t>
+          <t>Market parity — better product, not cheaper (locked).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Captive capture rate (A′ corridors)</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="n">
-        <v>0.9</v>
+          <t>Diesel CO₂ per gallon</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n">
+        <v>10.21</v>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
+          <t>kg/gal</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>US EPA: 10.21 kg CO2 per gallon marine/diesel</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>OPEX defaults  (global fallbacks — localized energy, crew, berth admin on Country opex tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Conf.</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Source / note</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Vessel insurance — H&amp;M + P&amp;I (% of CAPEX/yr)</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr"/>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>Sole-operator water-access-only transfer legs (captive:true or luxury_charter/hospitality archetype): Navier IS the transfer fleet — capture ~90%. Applied per-row in the Capture % column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Discount factor (vs comparable fare)</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>frac</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>Market parity — better product, not cheaper (locked).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Diesel CO₂ per gallon</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>kg/gal</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>US EPA: 10.21 kg CO2 per gallon marine/diesel</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Utilization scenarios  (the two levers we flex)</t>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Commercial vessel H&amp;M + P&amp;I ~2.5%/yr of regional CAPEX. Separate from berth/port admin in Country opex (Jaideep 2026-06-19).. Multiplied by regional CAPEX (Country opex col G). Not included in berth/port admin.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Fast-charge berth &amp; demand charges (global default)</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Dedicated fast-charge berth slot + utility demand charges. Excludes per-kWh propulsion energy and berth/port admin (Jaideep 2026-06-19). L3-overridable per market.. Dedicated charge berth + utility demand charges. Excludes per-kWh propulsion energy and berth/port admin. L3-overridable per market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Utilization scenarios  (load factor + revenue-leg factor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Load factor</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>Rev-leg factor</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr"/>
-      <c r="E30" s="10" t="inlineStr"/>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr"/>
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>THIN</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n">
+      <c r="B34" s="19" t="n">
         <v>0.45</v>
       </c>
-      <c r="C31" s="19" t="n">
+      <c r="C34" s="19" t="n">
         <v>0.55</v>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F34" s="14" t="inlineStr">
         <is>
           <t>thin/one-way/seasonal corridor — conservative floor</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n">
+      <c r="B35" s="19" t="n">
         <v>0.55</v>
       </c>
-      <c r="C32" s="19" t="n">
+      <c r="C35" s="19" t="n">
         <v>0.65</v>
       </c>
-      <c r="F32" s="14" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t>HEADLINE — realistic busy two-way corridor</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>FULL</t>
         </is>
       </c>
-      <c r="B33" s="19" t="n">
+      <c r="B36" s="19" t="n">
         <v>0.7</v>
       </c>
-      <c r="C33" s="19" t="n">
+      <c r="C36" s="19" t="n">
         <v>0.75</v>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F36" s="14" t="inlineStr">
         <is>
           <t>mature/dense corridor — optimistic ceiling</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>SCENARIO (toggle me)</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>← set THIN / MID / FULL</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Selected load factor</t>
         </is>
       </c>
-      <c r="B36" s="23">
-        <f>VLOOKUP(scenario,'Assumptions'!$A$31:$C$33,2,FALSE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="B39" s="23">
+        <f>VLOOKUP(scenario,'Assumptions'!$A$34:$C$36,2,FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Selected rev-leg factor</t>
         </is>
       </c>
-      <c r="B37" s="23">
-        <f>VLOOKUP(scenario,'Assumptions'!$A$31:$C$33,3,FALSE)</f>
+      <c r="B40" s="23">
+        <f>VLOOKUP(scenario,'Assumptions'!$A$34:$C$36,3,FALSE)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A3:F3"/>
+  <mergeCells count="5">
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"THIN,MID,FULL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1724,7 +1823,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Country opex — L3 localized layer (VLOOKUP target for the engine)</t>
+          <t>Country opex — localized inputs (crew, energy, berth admin, CAPEX)</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1850,7 @@
       </c>
       <c r="E3" s="24" t="inlineStr">
         <is>
-          <t>Marina $/yr</t>
+          <t>Berth &amp; port admin $/yr</t>
         </is>
       </c>
       <c r="F3" s="24" t="inlineStr">
@@ -1766,7 +1865,7 @@
       </c>
       <c r="H3" s="24" t="inlineStr">
         <is>
-          <t>Source notes (captain | energy | marina)</t>
+          <t>Source notes (crew | energy | berth admin)</t>
         </is>
       </c>
     </row>
@@ -1899,10 +1998,10 @@
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
     <col width="9" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
     <col width="11" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -2063,7 +2162,7 @@
       </c>
       <c r="W3" s="24" t="inlineStr">
         <is>
-          <t>Marina/yr</t>
+          <t>Berth &amp; port admin/yr</t>
         </is>
       </c>
       <c r="X3" s="24" t="inlineStr">
@@ -2073,12 +2172,12 @@
       </c>
       <c r="Y3" s="24" t="inlineStr">
         <is>
-          <t>Insurance/yr</t>
+          <t>Vessel insurance/yr</t>
         </is>
       </c>
       <c r="Z3" s="24" t="inlineStr">
         <is>
-          <t>Charge+berth/yr</t>
+          <t>Fast-charge berth/yr</t>
         </is>
       </c>
       <c r="AA3" s="24" t="inlineStr">

--- a/finance/_refresh_yassir.xlsx
+++ b/finance/_refresh_yassir.xlsx
@@ -45,8 +45,8 @@
     <definedName name="load_sel">'Assumptions'!$B$39</definedName>
     <definedName name="revleg_sel">'Assumptions'!$B$40</definedName>
     <definedName name="country_opex">'Country opex'!$A$4:$G$6</definedName>
-    <definedName name="som_floor_fleet">'Corridor economics'!$D$27</definedName>
-    <definedName name="som_floor_rev">'Corridor economics'!$E$27</definedName>
+    <definedName name="som_floor_fleet">'Corridor economics'!$D$28</definedName>
+    <definedName name="som_floor_rev">'Corridor economics'!$E$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -188,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -324,6 +324,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1973,7 +1979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2018,14 +2024,15 @@
     <col width="9" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
     <col width="26" customWidth="1" min="42" max="42"/>
-    <col width="16" customWidth="1" min="43" max="43"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
     <col width="16" customWidth="1" min="44" max="44"/>
-    <col width="9" customWidth="1" min="45" max="45"/>
+    <col width="16" customWidth="1" min="45" max="45"/>
     <col width="9" customWidth="1" min="46" max="46"/>
     <col width="9" customWidth="1" min="47" max="47"/>
     <col width="9" customWidth="1" min="48" max="48"/>
-    <col width="50" customWidth="1" min="49" max="49"/>
+    <col width="9" customWidth="1" min="49" max="49"/>
     <col width="50" customWidth="1" min="50" max="50"/>
+    <col width="50" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2262,40 +2269,45 @@
       </c>
       <c r="AQ3" s="24" t="inlineStr">
         <is>
+          <t>Floor bucket (aggregate status)</t>
+        </is>
+      </c>
+      <c r="AR3" s="24" t="inlineStr">
+        <is>
           <t>Forward SAM (2030-dated; held OUT of grounded floor)</t>
         </is>
       </c>
-      <c r="AR3" s="24" t="inlineStr">
+      <c r="AS3" s="24" t="inlineStr">
         <is>
           <t>Upside tier (LB-99; held OUT of grounded floor)</t>
         </is>
       </c>
-      <c r="AS3" s="24" t="inlineStr">
+      <c r="AT3" s="24" t="inlineStr">
         <is>
           <t>Fleet ceiling (captive villas/25)</t>
         </is>
       </c>
-      <c r="AT3" s="24" t="inlineStr">
+      <c r="AU3" s="24" t="inlineStr">
         <is>
           <t>Payback THIN</t>
         </is>
       </c>
-      <c r="AU3" s="24" t="inlineStr">
+      <c r="AV3" s="24" t="inlineStr">
         <is>
           <t>Payback MID</t>
         </is>
       </c>
-      <c r="AV3" s="24" t="inlineStr">
+      <c r="AW3" s="24" t="inlineStr">
         <is>
           <t>Payback FULL</t>
         </is>
       </c>
-      <c r="AW3" s="24" t="inlineStr">
+      <c r="AX3" s="24" t="inlineStr">
         <is>
           <t>Fare source (provenance)</t>
         </is>
       </c>
-      <c r="AX3" s="24" t="inlineStr">
+      <c r="AY3" s="24" t="inlineStr">
         <is>
           <t>Demand source (provenance)</t>
         </is>
@@ -2437,7 +2449,7 @@
         <v/>
       </c>
       <c r="AL4" s="34">
-        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AS4="",9.9E+99,AS4),FLOOR(AK4/R4,1)))</f>
+        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AT4="",9.9E+99,AT4),FLOOR(AK4/R4,1)))</f>
         <v/>
       </c>
       <c r="AM4" s="38">
@@ -2445,7 +2457,7 @@
         <v/>
       </c>
       <c r="AN4" s="36">
-        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AS4="",9.9E+99,AS4),AK4/R4))</f>
+        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AT4="",9.9E+99,AT4),AK4/R4))</f>
         <v/>
       </c>
       <c r="AO4" s="38">
@@ -2453,27 +2465,32 @@
         <v/>
       </c>
       <c r="AP4" s="40" t="n"/>
-      <c r="AQ4" s="41" t="n"/>
+      <c r="AQ4" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR4" s="41" t="n"/>
-      <c r="AS4" s="42" t="n"/>
-      <c r="AT4" s="43">
+      <c r="AS4" s="41" t="n"/>
+      <c r="AT4" s="42" t="n"/>
+      <c r="AU4" s="43">
         <f>IF(((S4*pax_cap*load_thin*ROUND(K4*L4*revleg_thin,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_thin,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_thin*ROUND(K4*L4*revleg_thin,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_thin,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AU4" s="43">
+      <c r="AV4" s="43">
         <f>IF(((S4*pax_cap*load_mid*ROUND(K4*L4*revleg_mid,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_mid,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_mid*ROUND(K4*L4*revleg_mid,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_mid,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AV4" s="43">
+      <c r="AW4" s="43">
         <f>IF(((S4*pax_cap*load_full*ROUND(K4*L4*revleg_full,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_full,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_full*ROUND(K4*L4*revleg_full,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_full,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AW4" s="44" t="inlineStr">
+      <c r="AX4" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">[LB-255 PREMIUM RE-FARE: subsidized comparable $3.7 lifted to premium on-demand floor $18.0] </t>
         </is>
       </c>
-      <c r="AX4" s="44" t="n"/>
+      <c r="AY4" s="44" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="29" t="inlineStr">
@@ -2509,7 +2526,7 @@
         <v/>
       </c>
       <c r="K5" s="34">
-        <f>MIN(24,FLOOR(60*service_hr/J5,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J5,1))</f>
         <v/>
       </c>
       <c r="L5" s="34">
@@ -2607,7 +2624,7 @@
         <v/>
       </c>
       <c r="AL5" s="34">
-        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AS5="",9.9E+99,AS5),FLOOR(AK5/R5,1)))</f>
+        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AT5="",9.9E+99,AT5),FLOOR(AK5/R5,1)))</f>
         <v/>
       </c>
       <c r="AM5" s="38">
@@ -2615,7 +2632,7 @@
         <v/>
       </c>
       <c r="AN5" s="36">
-        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AS5="",9.9E+99,AS5),AK5/R5))</f>
+        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AT5="",9.9E+99,AT5),AK5/R5))</f>
         <v/>
       </c>
       <c r="AO5" s="38">
@@ -2623,23 +2640,28 @@
         <v/>
       </c>
       <c r="AP5" s="40" t="n"/>
-      <c r="AQ5" s="41" t="n"/>
+      <c r="AQ5" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR5" s="41" t="n"/>
-      <c r="AS5" s="42" t="n"/>
-      <c r="AT5" s="43">
+      <c r="AS5" s="41" t="n"/>
+      <c r="AT5" s="42" t="n"/>
+      <c r="AU5" s="43">
         <f>IF(((S5*pax_cap*load_thin*ROUND(K5*L5*revleg_thin,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_thin,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_thin*ROUND(K5*L5*revleg_thin,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_thin,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AU5" s="43">
+      <c r="AV5" s="43">
         <f>IF(((S5*pax_cap*load_mid*ROUND(K5*L5*revleg_mid,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_mid,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_mid*ROUND(K5*L5*revleg_mid,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_mid,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AV5" s="43">
+      <c r="AW5" s="43">
         <f>IF(((S5*pax_cap*load_full*ROUND(K5*L5*revleg_full,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_full,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_full*ROUND(K5*L5*revleg_full,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_full,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AW5" s="44" t="n"/>
       <c r="AX5" s="44" t="n"/>
+      <c r="AY5" s="44" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
@@ -2654,25 +2676,15 @@
       </c>
       <c r="C6" s="30" t="inlineStr">
         <is>
-          <t>Tangier Marina Bay → Tarifa (cross-strait excluded)</t>
+          <t>Rabat → Sale</t>
         </is>
       </c>
       <c r="D6" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="F6" s="32" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="G6" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="26" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="32" t="n"/>
       <c r="H6" s="19" t="n">
         <v>1</v>
       </c>
@@ -2685,7 +2697,7 @@
         <v/>
       </c>
       <c r="K6" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J6,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J6,1))</f>
         <v/>
       </c>
       <c r="L6" s="34">
@@ -2772,9 +2784,7 @@
         <f>((D6*O6/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D6*O6*VLOOKUP(B6,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG6" s="31" t="n">
-        <v>760778</v>
-      </c>
+      <c r="AG6" s="31" t="n"/>
       <c r="AH6" s="32" t="n"/>
       <c r="AI6" s="32" t="n"/>
       <c r="AJ6" s="39" t="n">
@@ -2785,7 +2795,7 @@
         <v/>
       </c>
       <c r="AL6" s="34">
-        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AS6="",9.9E+99,AS6),FLOOR(AK6/R6,1)))</f>
+        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AT6="",9.9E+99,AT6),FLOOR(AK6/R6,1)))</f>
         <v/>
       </c>
       <c r="AM6" s="38">
@@ -2793,7 +2803,7 @@
         <v/>
       </c>
       <c r="AN6" s="36">
-        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AS6="",9.9E+99,AS6),AK6/R6))</f>
+        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AT6="",9.9E+99,AT6),AK6/R6))</f>
         <v/>
       </c>
       <c r="AO6" s="38">
@@ -2801,27 +2811,28 @@
         <v/>
       </c>
       <c r="AP6" s="40" t="n"/>
-      <c r="AQ6" s="41" t="n"/>
+      <c r="AQ6" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR6" s="41" t="n"/>
-      <c r="AS6" s="42" t="n"/>
-      <c r="AT6" s="43">
+      <c r="AS6" s="41" t="n"/>
+      <c r="AT6" s="42" t="n"/>
+      <c r="AU6" s="43">
         <f>IF(((S6*pax_cap*load_thin*ROUND(K6*L6*revleg_thin,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_thin,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_thin*ROUND(K6*L6*revleg_thin,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_thin,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AU6" s="43">
+      <c r="AV6" s="43">
         <f>IF(((S6*pax_cap*load_mid*ROUND(K6*L6*revleg_mid,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_mid,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_mid*ROUND(K6*L6*revleg_mid,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_mid,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AV6" s="43">
+      <c r="AW6" s="43">
         <f>IF(((S6*pax_cap*load_full*ROUND(K6*L6*revleg_full,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_full,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_full*ROUND(K6*L6*revleg_full,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_full,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AW6" s="44" t="inlineStr">
-        <is>
-          <t>PREMIUM tier: standard adult FOOT-PASSENGER one-way fast-ferry fare Tarifa&lt;-&gt;Tangier Ville ~EUR 40.25 (traveller-reported foot fare) x 1.08 = ~$43.5; DirectFerries lists 'from $46'. THIS is the Navier-modeled per-seat tier.</t>
-        </is>
-      </c>
       <c r="AX6" s="44" t="n"/>
+      <c r="AY6" s="44" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
@@ -2836,15 +2847,25 @@
       </c>
       <c r="C7" s="30" t="inlineStr">
         <is>
-          <t>Agadir Marina → Taghazout</t>
+          <t>Tangier Marina Bay → Tarifa (cross-strait excluded)</t>
         </is>
       </c>
       <c r="D7" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" s="26" t="n"/>
-      <c r="F7" s="32" t="n"/>
-      <c r="G7" s="32" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F7" s="32" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G7" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
       <c r="H7" s="19" t="n">
         <v>1</v>
       </c>
@@ -2945,7 +2966,7 @@
         <v/>
       </c>
       <c r="AG7" s="31" t="n">
-        <v>77500</v>
+        <v>760778</v>
       </c>
       <c r="AH7" s="32" t="n"/>
       <c r="AI7" s="32" t="n"/>
@@ -2957,7 +2978,7 @@
         <v/>
       </c>
       <c r="AL7" s="34">
-        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AS7="",9.9E+99,AS7),FLOOR(AK7/R7,1)))</f>
+        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AT7="",9.9E+99,AT7),FLOOR(AK7/R7,1)))</f>
         <v/>
       </c>
       <c r="AM7" s="38">
@@ -2965,7 +2986,7 @@
         <v/>
       </c>
       <c r="AN7" s="36">
-        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AS7="",9.9E+99,AS7),AK7/R7))</f>
+        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AT7="",9.9E+99,AT7),AK7/R7))</f>
         <v/>
       </c>
       <c r="AO7" s="38">
@@ -2973,23 +2994,32 @@
         <v/>
       </c>
       <c r="AP7" s="40" t="n"/>
-      <c r="AQ7" s="41" t="n"/>
+      <c r="AQ7" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR7" s="41" t="n"/>
-      <c r="AS7" s="42" t="n"/>
-      <c r="AT7" s="43">
+      <c r="AS7" s="41" t="n"/>
+      <c r="AT7" s="42" t="n"/>
+      <c r="AU7" s="43">
         <f>IF(((S7*pax_cap*load_thin*ROUND(K7*L7*revleg_thin,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_thin,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_thin*ROUND(K7*L7*revleg_thin,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_thin,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AU7" s="43">
+      <c r="AV7" s="43">
         <f>IF(((S7*pax_cap*load_mid*ROUND(K7*L7*revleg_mid,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_mid,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_mid*ROUND(K7*L7*revleg_mid,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_mid,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AV7" s="43">
+      <c r="AW7" s="43">
         <f>IF(((S7*pax_cap*load_full*ROUND(K7*L7*revleg_full,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_full,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_full*ROUND(K7*L7*revleg_full,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_full,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AW7" s="44" t="n"/>
-      <c r="AX7" s="44" t="n"/>
+      <c r="AX7" s="44" t="inlineStr">
+        <is>
+          <t>PREMIUM tier: standard adult FOOT-PASSENGER one-way fast-ferry fare Tarifa&lt;-&gt;Tangier Ville ~EUR 40.25 (traveller-reported foot fare) x 1.08 = ~$43.5; DirectFerries lists 'from $46'. THIS is the Navier-modeled per-seat tier.</t>
+        </is>
+      </c>
+      <c r="AY7" s="44" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
@@ -3004,25 +3034,15 @@
       </c>
       <c r="C8" s="30" t="inlineStr">
         <is>
-          <t>Tanger Med (Ksar el Majaz) → Algeciras (Spain)</t>
+          <t>Agadir Marina → Taghazout</t>
         </is>
       </c>
       <c r="D8" s="31" t="n">
-        <v>13</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>38</v>
-      </c>
-      <c r="F8" s="32" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="G8" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="E8" s="26" t="n"/>
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="32" t="n"/>
       <c r="H8" s="19" t="n">
         <v>1</v>
       </c>
@@ -3123,7 +3143,7 @@
         <v/>
       </c>
       <c r="AG8" s="31" t="n">
-        <v>1610211</v>
+        <v>77500</v>
       </c>
       <c r="AH8" s="32" t="n"/>
       <c r="AI8" s="32" t="n"/>
@@ -3135,7 +3155,7 @@
         <v/>
       </c>
       <c r="AL8" s="34">
-        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AS8="",9.9E+99,AS8),FLOOR(AK8/R8,1)))</f>
+        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AT8="",9.9E+99,AT8),FLOOR(AK8/R8,1)))</f>
         <v/>
       </c>
       <c r="AM8" s="38">
@@ -3143,7 +3163,7 @@
         <v/>
       </c>
       <c r="AN8" s="36">
-        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AS8="",9.9E+99,AS8),AK8/R8))</f>
+        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AT8="",9.9E+99,AT8),AK8/R8))</f>
         <v/>
       </c>
       <c r="AO8" s="38">
@@ -3151,27 +3171,28 @@
         <v/>
       </c>
       <c r="AP8" s="40" t="n"/>
-      <c r="AQ8" s="41" t="n"/>
+      <c r="AQ8" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR8" s="41" t="n"/>
-      <c r="AS8" s="42" t="n"/>
-      <c r="AT8" s="43">
+      <c r="AS8" s="41" t="n"/>
+      <c r="AT8" s="42" t="n"/>
+      <c r="AU8" s="43">
         <f>IF(((S8*pax_cap*load_thin*ROUND(K8*L8*revleg_thin,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_thin,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_thin*ROUND(K8*L8*revleg_thin,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_thin,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AU8" s="43">
+      <c r="AV8" s="43">
         <f>IF(((S8*pax_cap*load_mid*ROUND(K8*L8*revleg_mid,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_mid,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_mid*ROUND(K8*L8*revleg_mid,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_mid,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AV8" s="43">
+      <c r="AW8" s="43">
         <f>IF(((S8*pax_cap*load_full*ROUND(K8*L8*revleg_full,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_full,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_full*ROUND(K8*L8*revleg_full,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_full,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AW8" s="44" t="inlineStr">
-        <is>
-          <t>PREMIUM tier: standard adult FOOT-PASSENGER one-way Tanger Med&lt;-&gt;Algeciras ~EUR 35 x 1.08 = ~$38 (Strait fast-ferry foot fares cluster EUR 30-40).</t>
-        </is>
-      </c>
       <c r="AX8" s="44" t="n"/>
+      <c r="AY8" s="44" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
@@ -3305,7 +3326,7 @@
         <v/>
       </c>
       <c r="AL9" s="34">
-        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AS9="",9.9E+99,AS9),FLOOR(AK9/R9,1)))</f>
+        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AT9="",9.9E+99,AT9),FLOOR(AK9/R9,1)))</f>
         <v/>
       </c>
       <c r="AM9" s="38">
@@ -3313,7 +3334,7 @@
         <v/>
       </c>
       <c r="AN9" s="36">
-        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AS9="",9.9E+99,AS9),AK9/R9))</f>
+        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AT9="",9.9E+99,AT9),AK9/R9))</f>
         <v/>
       </c>
       <c r="AO9" s="38">
@@ -3321,23 +3342,28 @@
         <v/>
       </c>
       <c r="AP9" s="40" t="n"/>
-      <c r="AQ9" s="41" t="n"/>
+      <c r="AQ9" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR9" s="41" t="n"/>
-      <c r="AS9" s="42" t="n"/>
-      <c r="AT9" s="43">
+      <c r="AS9" s="41" t="n"/>
+      <c r="AT9" s="42" t="n"/>
+      <c r="AU9" s="43">
         <f>IF(((S9*pax_cap*load_thin*ROUND(K9*L9*revleg_thin,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_thin,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((S9*pax_cap*load_thin*ROUND(K9*L9*revleg_thin,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_thin,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9)))</f>
         <v/>
       </c>
-      <c r="AU9" s="43">
+      <c r="AV9" s="43">
         <f>IF(((S9*pax_cap*load_mid*ROUND(K9*L9*revleg_mid,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_mid,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((S9*pax_cap*load_mid*ROUND(K9*L9*revleg_mid,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_mid,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9)))</f>
         <v/>
       </c>
-      <c r="AV9" s="43">
+      <c r="AW9" s="43">
         <f>IF(((S9*pax_cap*load_full*ROUND(K9*L9*revleg_full,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_full,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((S9*pax_cap*load_full*ROUND(K9*L9*revleg_full,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_full,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9)))</f>
         <v/>
       </c>
-      <c r="AW9" s="44" t="n"/>
       <c r="AX9" s="44" t="n"/>
+      <c r="AY9" s="44" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
@@ -3352,15 +3378,25 @@
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>Al Hoceima → Cala Iris</t>
+          <t>Tanger Med (Ksar el Majaz) → Algeciras (Spain)</t>
         </is>
       </c>
       <c r="D10" s="31" t="n">
-        <v>16</v>
-      </c>
-      <c r="E10" s="26" t="n"/>
-      <c r="F10" s="32" t="n"/>
-      <c r="G10" s="32" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="F10" s="32" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G10" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
       <c r="H10" s="19" t="n">
         <v>1</v>
       </c>
@@ -3373,7 +3409,7 @@
         <v/>
       </c>
       <c r="K10" s="34">
-        <f>MIN(24,FLOOR(60*service_hr/J10,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J10,1))</f>
         <v/>
       </c>
       <c r="L10" s="34">
@@ -3460,7 +3496,9 @@
         <f>((D10*O10/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D10*O10*VLOOKUP(B10,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG10" s="31" t="n"/>
+      <c r="AG10" s="31" t="n">
+        <v>1610211</v>
+      </c>
       <c r="AH10" s="32" t="n"/>
       <c r="AI10" s="32" t="n"/>
       <c r="AJ10" s="39" t="n">
@@ -3471,7 +3509,7 @@
         <v/>
       </c>
       <c r="AL10" s="34">
-        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AS10="",9.9E+99,AS10),FLOOR(AK10/R10,1)))</f>
+        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AT10="",9.9E+99,AT10),FLOOR(AK10/R10,1)))</f>
         <v/>
       </c>
       <c r="AM10" s="38">
@@ -3479,7 +3517,7 @@
         <v/>
       </c>
       <c r="AN10" s="36">
-        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AS10="",9.9E+99,AS10),AK10/R10))</f>
+        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AT10="",9.9E+99,AT10),AK10/R10))</f>
         <v/>
       </c>
       <c r="AO10" s="38">
@@ -3487,23 +3525,32 @@
         <v/>
       </c>
       <c r="AP10" s="40" t="n"/>
-      <c r="AQ10" s="41" t="n"/>
+      <c r="AQ10" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR10" s="41" t="n"/>
-      <c r="AS10" s="42" t="n"/>
-      <c r="AT10" s="43">
+      <c r="AS10" s="41" t="n"/>
+      <c r="AT10" s="42" t="n"/>
+      <c r="AU10" s="43">
         <f>IF(((S10*pax_cap*load_thin*ROUND(K10*L10*revleg_thin,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_thin,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((S10*pax_cap*load_thin*ROUND(K10*L10*revleg_thin,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_thin,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10)))</f>
         <v/>
       </c>
-      <c r="AU10" s="43">
+      <c r="AV10" s="43">
         <f>IF(((S10*pax_cap*load_mid*ROUND(K10*L10*revleg_mid,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_mid,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((S10*pax_cap*load_mid*ROUND(K10*L10*revleg_mid,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_mid,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10)))</f>
         <v/>
       </c>
-      <c r="AV10" s="43">
+      <c r="AW10" s="43">
         <f>IF(((S10*pax_cap*load_full*ROUND(K10*L10*revleg_full,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_full,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((S10*pax_cap*load_full*ROUND(K10*L10*revleg_full,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_full,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10)))</f>
         <v/>
       </c>
-      <c r="AW10" s="44" t="n"/>
-      <c r="AX10" s="44" t="n"/>
+      <c r="AX10" s="44" t="inlineStr">
+        <is>
+          <t>PREMIUM tier: standard adult FOOT-PASSENGER one-way Tanger Med&lt;-&gt;Algeciras ~EUR 35 x 1.08 = ~$38 (Strait fast-ferry foot fares cluster EUR 30-40).</t>
+        </is>
+      </c>
+      <c r="AY10" s="44" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
@@ -3518,25 +3565,15 @@
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>Tanger Med → Ceuta (Spanish enclave)</t>
+          <t>Al Hoceima → Cala Iris</t>
         </is>
       </c>
       <c r="D11" s="31" t="n">
-        <v>22</v>
-      </c>
-      <c r="E11" s="26" t="n">
-        <v>36</v>
-      </c>
-      <c r="F11" s="32" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="G11" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="32" t="n"/>
+      <c r="G11" s="32" t="n"/>
       <c r="H11" s="19" t="n">
         <v>1</v>
       </c>
@@ -3549,7 +3586,7 @@
         <v/>
       </c>
       <c r="K11" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J11,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J11,1))</f>
         <v/>
       </c>
       <c r="L11" s="34">
@@ -3647,7 +3684,7 @@
         <v/>
       </c>
       <c r="AL11" s="34">
-        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AS11="",9.9E+99,AS11),FLOOR(AK11/R11,1)))</f>
+        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AT11="",9.9E+99,AT11),FLOOR(AK11/R11,1)))</f>
         <v/>
       </c>
       <c r="AM11" s="38">
@@ -3655,7 +3692,7 @@
         <v/>
       </c>
       <c r="AN11" s="36">
-        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AS11="",9.9E+99,AS11),AK11/R11))</f>
+        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AT11="",9.9E+99,AT11),AK11/R11))</f>
         <v/>
       </c>
       <c r="AO11" s="38">
@@ -3663,27 +3700,28 @@
         <v/>
       </c>
       <c r="AP11" s="40" t="n"/>
-      <c r="AQ11" s="41" t="n"/>
+      <c r="AQ11" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR11" s="41" t="n"/>
-      <c r="AS11" s="42" t="n"/>
-      <c r="AT11" s="43">
+      <c r="AS11" s="41" t="n"/>
+      <c r="AT11" s="42" t="n"/>
+      <c r="AU11" s="43">
         <f>IF(((S11*pax_cap*load_thin*ROUND(K11*L11*revleg_thin,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_thin,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((S11*pax_cap*load_thin*ROUND(K11*L11*revleg_thin,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_thin,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11)))</f>
         <v/>
       </c>
-      <c r="AU11" s="43">
+      <c r="AV11" s="43">
         <f>IF(((S11*pax_cap*load_mid*ROUND(K11*L11*revleg_mid,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_mid,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((S11*pax_cap*load_mid*ROUND(K11*L11*revleg_mid,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_mid,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11)))</f>
         <v/>
       </c>
-      <c r="AV11" s="43">
+      <c r="AW11" s="43">
         <f>IF(((S11*pax_cap*load_full*ROUND(K11*L11*revleg_full,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_full,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((S11*pax_cap*load_full*ROUND(K11*L11*revleg_full,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_full,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11)))</f>
         <v/>
       </c>
-      <c r="AW11" s="44" t="inlineStr">
-        <is>
-          <t>PREMIUM tier (nearest comparable = Algeciras&lt;-&gt;Ceuta fast ferry): avg foot-passenger fare ~EUR 33 x 1.08 ~= $36 (one-way ~EUR 25-35), 60 min fast ferry.</t>
-        </is>
-      </c>
       <c r="AX11" s="44" t="n"/>
+      <c r="AY11" s="44" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="29" t="inlineStr">
@@ -3698,15 +3736,25 @@
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>Casablanca → Rabat</t>
+          <t>Tanger Med → Ceuta (Spanish enclave)</t>
         </is>
       </c>
       <c r="D12" s="31" t="n">
-        <v>46</v>
-      </c>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="32" t="n"/>
-      <c r="G12" s="32" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>36</v>
+      </c>
+      <c r="F12" s="32" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
       <c r="H12" s="19" t="n">
         <v>1</v>
       </c>
@@ -3719,7 +3767,7 @@
         <v/>
       </c>
       <c r="K12" s="34">
-        <f>MIN(24,FLOOR(60*service_hr/J12,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J12,1))</f>
         <v/>
       </c>
       <c r="L12" s="34">
@@ -3806,9 +3854,7 @@
         <f>((D12*O12/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D12*O12*VLOOKUP(B12,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG12" s="31" t="n">
-        <v>165000</v>
-      </c>
+      <c r="AG12" s="31" t="n"/>
       <c r="AH12" s="32" t="n"/>
       <c r="AI12" s="32" t="n"/>
       <c r="AJ12" s="39" t="n">
@@ -3819,7 +3865,7 @@
         <v/>
       </c>
       <c r="AL12" s="34">
-        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AS12="",9.9E+99,AS12),FLOOR(AK12/R12,1)))</f>
+        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AT12="",9.9E+99,AT12),FLOOR(AK12/R12,1)))</f>
         <v/>
       </c>
       <c r="AM12" s="38">
@@ -3827,7 +3873,7 @@
         <v/>
       </c>
       <c r="AN12" s="36">
-        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AS12="",9.9E+99,AS12),AK12/R12))</f>
+        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AT12="",9.9E+99,AT12),AK12/R12))</f>
         <v/>
       </c>
       <c r="AO12" s="38">
@@ -3835,42 +3881,51 @@
         <v/>
       </c>
       <c r="AP12" s="40" t="n"/>
-      <c r="AQ12" s="41" t="n"/>
+      <c r="AQ12" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR12" s="41" t="n"/>
-      <c r="AS12" s="42" t="n"/>
-      <c r="AT12" s="43">
+      <c r="AS12" s="41" t="n"/>
+      <c r="AT12" s="42" t="n"/>
+      <c r="AU12" s="43">
         <f>IF(((S12*pax_cap*load_thin*ROUND(K12*L12*revleg_thin,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_thin,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((S12*pax_cap*load_thin*ROUND(K12*L12*revleg_thin,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_thin,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12)))</f>
         <v/>
       </c>
-      <c r="AU12" s="43">
+      <c r="AV12" s="43">
         <f>IF(((S12*pax_cap*load_mid*ROUND(K12*L12*revleg_mid,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_mid,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((S12*pax_cap*load_mid*ROUND(K12*L12*revleg_mid,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_mid,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12)))</f>
         <v/>
       </c>
-      <c r="AV12" s="43">
+      <c r="AW12" s="43">
         <f>IF(((S12*pax_cap*load_full*ROUND(K12*L12*revleg_full,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_full,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((S12*pax_cap*load_full*ROUND(K12*L12*revleg_full,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_full,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12)))</f>
         <v/>
       </c>
-      <c r="AW12" s="44" t="n"/>
-      <c r="AX12" s="44" t="n"/>
+      <c r="AX12" s="44" t="inlineStr">
+        <is>
+          <t>PREMIUM tier (nearest comparable = Algeciras&lt;-&gt;Ceuta fast ferry): avg foot-passenger fare ~EUR 33 x 1.08 ~= $36 (one-way ~EUR 25-35), 60 min fast ferry.</t>
+        </is>
+      </c>
+      <c r="AY12" s="44" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="29" t="inlineStr">
         <is>
-          <t>Yassir Tunisia</t>
+          <t>Yassir Morocco</t>
         </is>
       </c>
       <c r="B13" s="29" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C13" s="30" t="inlineStr">
         <is>
-          <t>Jorf (mainland) → Ajim (Djerba Island)</t>
+          <t>Casablanca → Rabat</t>
         </is>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.1</v>
+        <v>46</v>
       </c>
       <c r="E13" s="26" t="n"/>
       <c r="F13" s="32" t="n"/>
@@ -3887,7 +3942,7 @@
         <v/>
       </c>
       <c r="K13" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J13,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J13,1))</f>
         <v/>
       </c>
       <c r="L13" s="34">
@@ -3975,7 +4030,7 @@
         <v/>
       </c>
       <c r="AG13" s="31" t="n">
-        <v>2463750</v>
+        <v>165000</v>
       </c>
       <c r="AH13" s="32" t="n"/>
       <c r="AI13" s="32" t="n"/>
@@ -3987,7 +4042,7 @@
         <v/>
       </c>
       <c r="AL13" s="34">
-        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AS13="",9.9E+99,AS13),FLOOR(AK13/R13,1)))</f>
+        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AT13="",9.9E+99,AT13),FLOOR(AK13/R13,1)))</f>
         <v/>
       </c>
       <c r="AM13" s="38">
@@ -3995,7 +4050,7 @@
         <v/>
       </c>
       <c r="AN13" s="36">
-        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AS13="",9.9E+99,AS13),AK13/R13))</f>
+        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AT13="",9.9E+99,AT13),AK13/R13))</f>
         <v/>
       </c>
       <c r="AO13" s="38">
@@ -4003,23 +4058,28 @@
         <v/>
       </c>
       <c r="AP13" s="40" t="n"/>
-      <c r="AQ13" s="41" t="n"/>
+      <c r="AQ13" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR13" s="41" t="n"/>
-      <c r="AS13" s="42" t="n"/>
-      <c r="AT13" s="43">
+      <c r="AS13" s="41" t="n"/>
+      <c r="AT13" s="42" t="n"/>
+      <c r="AU13" s="43">
         <f>IF(((S13*pax_cap*load_thin*ROUND(K13*L13*revleg_thin,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_thin,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((S13*pax_cap*load_thin*ROUND(K13*L13*revleg_thin,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_thin,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13)))</f>
         <v/>
       </c>
-      <c r="AU13" s="43">
+      <c r="AV13" s="43">
         <f>IF(((S13*pax_cap*load_mid*ROUND(K13*L13*revleg_mid,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_mid,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((S13*pax_cap*load_mid*ROUND(K13*L13*revleg_mid,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_mid,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13)))</f>
         <v/>
       </c>
-      <c r="AV13" s="43">
+      <c r="AW13" s="43">
         <f>IF(((S13*pax_cap*load_full*ROUND(K13*L13*revleg_full,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_full,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((S13*pax_cap*load_full*ROUND(K13*L13*revleg_full,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_full,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13)))</f>
         <v/>
       </c>
-      <c r="AW13" s="44" t="n"/>
       <c r="AX13" s="44" t="n"/>
+      <c r="AY13" s="44" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
@@ -4034,25 +4094,15 @@
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
-          <t>La Goulette → Sidi Bou Said</t>
+          <t>Jorf (mainland) → Ajim (Djerba Island)</t>
         </is>
       </c>
       <c r="D14" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" s="26" t="n">
-        <v>27</v>
-      </c>
-      <c r="F14" s="32" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="G14" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="E14" s="26" t="n"/>
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="32" t="n"/>
       <c r="H14" s="19" t="n">
         <v>1</v>
       </c>
@@ -4153,7 +4203,7 @@
         <v/>
       </c>
       <c r="AG14" s="31" t="n">
-        <v>222000</v>
+        <v>2463750</v>
       </c>
       <c r="AH14" s="32" t="n"/>
       <c r="AI14" s="32" t="n"/>
@@ -4165,7 +4215,7 @@
         <v/>
       </c>
       <c r="AL14" s="34">
-        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AS14="",9.9E+99,AS14),FLOOR(AK14/R14,1)))</f>
+        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AT14="",9.9E+99,AT14),FLOOR(AK14/R14,1)))</f>
         <v/>
       </c>
       <c r="AM14" s="38">
@@ -4173,7 +4223,7 @@
         <v/>
       </c>
       <c r="AN14" s="36">
-        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AS14="",9.9E+99,AS14),AK14/R14))</f>
+        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AT14="",9.9E+99,AT14),AK14/R14))</f>
         <v/>
       </c>
       <c r="AO14" s="38">
@@ -4181,27 +4231,28 @@
         <v/>
       </c>
       <c r="AP14" s="40" t="n"/>
-      <c r="AQ14" s="41" t="n"/>
+      <c r="AQ14" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR14" s="41" t="n"/>
-      <c r="AS14" s="42" t="n"/>
-      <c r="AT14" s="43">
+      <c r="AS14" s="41" t="n"/>
+      <c r="AT14" s="42" t="n"/>
+      <c r="AU14" s="43">
         <f>IF(((S14*pax_cap*load_thin*ROUND(K14*L14*revleg_thin,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_thin,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((S14*pax_cap*load_thin*ROUND(K14*L14*revleg_thin,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_thin,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14)))</f>
         <v/>
       </c>
-      <c r="AU14" s="43">
+      <c r="AV14" s="43">
         <f>IF(((S14*pax_cap*load_mid*ROUND(K14*L14*revleg_mid,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_mid,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((S14*pax_cap*load_mid*ROUND(K14*L14*revleg_mid,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_mid,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14)))</f>
         <v/>
       </c>
-      <c r="AV14" s="43">
+      <c r="AW14" s="43">
         <f>IF(((S14*pax_cap*load_full*ROUND(K14*L14*revleg_full,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_full,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((S14*pax_cap*load_full*ROUND(K14*L14*revleg_full,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_full,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14)))</f>
         <v/>
       </c>
-      <c r="AW14" s="44" t="inlineStr">
-        <is>
-          <t>PREMIUM charter-divided tier: Gulf of Tunis / Sidi Bou Said per-seat excursion cruise ~EUR 25 (pirate-boat dinner cruise 'from EUR 30'; 3h marina cruise EUR 15-20) x 1.08 ~= $27. Nearest premium per-seat water product on this corridor; no scheduled fast catamaran exists.</t>
-        </is>
-      </c>
       <c r="AX14" s="44" t="n"/>
+      <c r="AY14" s="44" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="29" t="inlineStr">
@@ -4216,15 +4267,25 @@
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>Tunis (Tunis Marine) → La Goulette</t>
+          <t>La Goulette → Sidi Bou Said</t>
         </is>
       </c>
       <c r="D15" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="E15" s="26" t="n"/>
-      <c r="F15" s="32" t="n"/>
-      <c r="G15" s="32" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>27</v>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G15" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
       <c r="H15" s="19" t="n">
         <v>1</v>
       </c>
@@ -4237,7 +4298,7 @@
         <v/>
       </c>
       <c r="K15" s="34">
-        <f>MIN(24,FLOOR(60*service_hr/J15,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J15,1))</f>
         <v/>
       </c>
       <c r="L15" s="34">
@@ -4325,7 +4386,7 @@
         <v/>
       </c>
       <c r="AG15" s="31" t="n">
-        <v>296000</v>
+        <v>222000</v>
       </c>
       <c r="AH15" s="32" t="n"/>
       <c r="AI15" s="32" t="n"/>
@@ -4337,7 +4398,7 @@
         <v/>
       </c>
       <c r="AL15" s="34">
-        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AS15="",9.9E+99,AS15),FLOOR(AK15/R15,1)))</f>
+        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AT15="",9.9E+99,AT15),FLOOR(AK15/R15,1)))</f>
         <v/>
       </c>
       <c r="AM15" s="38">
@@ -4345,7 +4406,7 @@
         <v/>
       </c>
       <c r="AN15" s="36">
-        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AS15="",9.9E+99,AS15),AK15/R15))</f>
+        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AT15="",9.9E+99,AT15),AK15/R15))</f>
         <v/>
       </c>
       <c r="AO15" s="38">
@@ -4353,23 +4414,32 @@
         <v/>
       </c>
       <c r="AP15" s="40" t="n"/>
-      <c r="AQ15" s="41" t="n"/>
+      <c r="AQ15" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR15" s="41" t="n"/>
-      <c r="AS15" s="42" t="n"/>
-      <c r="AT15" s="43">
+      <c r="AS15" s="41" t="n"/>
+      <c r="AT15" s="42" t="n"/>
+      <c r="AU15" s="43">
         <f>IF(((S15*pax_cap*load_thin*ROUND(K15*L15*revleg_thin,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_thin,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((S15*pax_cap*load_thin*ROUND(K15*L15*revleg_thin,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_thin,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15)))</f>
         <v/>
       </c>
-      <c r="AU15" s="43">
+      <c r="AV15" s="43">
         <f>IF(((S15*pax_cap*load_mid*ROUND(K15*L15*revleg_mid,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_mid,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((S15*pax_cap*load_mid*ROUND(K15*L15*revleg_mid,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_mid,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15)))</f>
         <v/>
       </c>
-      <c r="AV15" s="43">
+      <c r="AW15" s="43">
         <f>IF(((S15*pax_cap*load_full*ROUND(K15*L15*revleg_full,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_full,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((S15*pax_cap*load_full*ROUND(K15*L15*revleg_full,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_full,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15)))</f>
         <v/>
       </c>
-      <c r="AW15" s="44" t="n"/>
-      <c r="AX15" s="44" t="n"/>
+      <c r="AX15" s="44" t="inlineStr">
+        <is>
+          <t>PREMIUM charter-divided tier: Gulf of Tunis / Sidi Bou Said per-seat excursion cruise ~EUR 25 (pirate-boat dinner cruise 'from EUR 30'; 3h marina cruise EUR 15-20) x 1.08 ~= $27. Nearest premium per-seat water product on this corridor; no scheduled fast catamaran exists.</t>
+        </is>
+      </c>
+      <c r="AY15" s="44" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="29" t="inlineStr">
@@ -4384,11 +4454,11 @@
       </c>
       <c r="C16" s="30" t="inlineStr">
         <is>
-          <t>Tunis (La Goulette) → La Marsa / Gammarth</t>
+          <t>Tunis (Tunis Marine) → La Goulette</t>
         </is>
       </c>
       <c r="D16" s="31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E16" s="26" t="n"/>
       <c r="F16" s="32" t="n"/>
@@ -4493,7 +4563,7 @@
         <v/>
       </c>
       <c r="AG16" s="31" t="n">
-        <v>222000</v>
+        <v>296000</v>
       </c>
       <c r="AH16" s="32" t="n"/>
       <c r="AI16" s="32" t="n"/>
@@ -4505,7 +4575,7 @@
         <v/>
       </c>
       <c r="AL16" s="34">
-        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AS16="",9.9E+99,AS16),FLOOR(AK16/R16,1)))</f>
+        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AT16="",9.9E+99,AT16),FLOOR(AK16/R16,1)))</f>
         <v/>
       </c>
       <c r="AM16" s="38">
@@ -4513,7 +4583,7 @@
         <v/>
       </c>
       <c r="AN16" s="36">
-        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AS16="",9.9E+99,AS16),AK16/R16))</f>
+        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AT16="",9.9E+99,AT16),AK16/R16))</f>
         <v/>
       </c>
       <c r="AO16" s="38">
@@ -4521,23 +4591,28 @@
         <v/>
       </c>
       <c r="AP16" s="40" t="n"/>
-      <c r="AQ16" s="41" t="n"/>
+      <c r="AQ16" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR16" s="41" t="n"/>
-      <c r="AS16" s="42" t="n"/>
-      <c r="AT16" s="43">
+      <c r="AS16" s="41" t="n"/>
+      <c r="AT16" s="42" t="n"/>
+      <c r="AU16" s="43">
         <f>IF(((S16*pax_cap*load_thin*ROUND(K16*L16*revleg_thin,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_thin,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16))&lt;=0,"",VLOOKUP(B16,country_opex,7,FALSE)/((S16*pax_cap*load_thin*ROUND(K16*L16*revleg_thin,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_thin,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16)))</f>
         <v/>
       </c>
-      <c r="AU16" s="43">
+      <c r="AV16" s="43">
         <f>IF(((S16*pax_cap*load_mid*ROUND(K16*L16*revleg_mid,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_mid,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16))&lt;=0,"",VLOOKUP(B16,country_opex,7,FALSE)/((S16*pax_cap*load_mid*ROUND(K16*L16*revleg_mid,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_mid,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16)))</f>
         <v/>
       </c>
-      <c r="AV16" s="43">
+      <c r="AW16" s="43">
         <f>IF(((S16*pax_cap*load_full*ROUND(K16*L16*revleg_full,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_full,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16))&lt;=0,"",VLOOKUP(B16,country_opex,7,FALSE)/((S16*pax_cap*load_full*ROUND(K16*L16*revleg_full,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_full,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16)))</f>
         <v/>
       </c>
-      <c r="AW16" s="44" t="n"/>
       <c r="AX16" s="44" t="n"/>
+      <c r="AY16" s="44" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
@@ -4552,25 +4627,15 @@
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>Yasmine Hammamet → Nabeul</t>
+          <t>Tunis (La Goulette) → La Marsa / Gammarth</t>
         </is>
       </c>
       <c r="D17" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="E17" s="26" t="n">
-        <v>22</v>
-      </c>
-      <c r="F17" s="32" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="G17" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+      <c r="E17" s="26" t="n"/>
+      <c r="F17" s="32" t="n"/>
+      <c r="G17" s="32" t="n"/>
       <c r="H17" s="19" t="n">
         <v>1</v>
       </c>
@@ -4583,7 +4648,7 @@
         <v/>
       </c>
       <c r="K17" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J17,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J17,1))</f>
         <v/>
       </c>
       <c r="L17" s="34">
@@ -4670,7 +4735,9 @@
         <f>((D17*O17/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D17*O17*VLOOKUP(B17,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG17" s="31" t="n"/>
+      <c r="AG17" s="31" t="n">
+        <v>222000</v>
+      </c>
       <c r="AH17" s="32" t="n"/>
       <c r="AI17" s="32" t="n"/>
       <c r="AJ17" s="39" t="n">
@@ -4681,7 +4748,7 @@
         <v/>
       </c>
       <c r="AL17" s="34">
-        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AS17="",9.9E+99,AS17),FLOOR(AK17/R17,1)))</f>
+        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AT17="",9.9E+99,AT17),FLOOR(AK17/R17,1)))</f>
         <v/>
       </c>
       <c r="AM17" s="38">
@@ -4689,7 +4756,7 @@
         <v/>
       </c>
       <c r="AN17" s="36">
-        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AS17="",9.9E+99,AS17),AK17/R17))</f>
+        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AT17="",9.9E+99,AT17),AK17/R17))</f>
         <v/>
       </c>
       <c r="AO17" s="38">
@@ -4697,27 +4764,28 @@
         <v/>
       </c>
       <c r="AP17" s="40" t="n"/>
-      <c r="AQ17" s="41" t="n"/>
+      <c r="AQ17" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR17" s="41" t="n"/>
-      <c r="AS17" s="42" t="n"/>
-      <c r="AT17" s="43">
+      <c r="AS17" s="41" t="n"/>
+      <c r="AT17" s="42" t="n"/>
+      <c r="AU17" s="43">
         <f>IF(((S17*pax_cap*load_thin*ROUND(K17*L17*revleg_thin,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_thin,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17))&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/((S17*pax_cap*load_thin*ROUND(K17*L17*revleg_thin,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_thin,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17)))</f>
         <v/>
       </c>
-      <c r="AU17" s="43">
+      <c r="AV17" s="43">
         <f>IF(((S17*pax_cap*load_mid*ROUND(K17*L17*revleg_mid,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_mid,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17))&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/((S17*pax_cap*load_mid*ROUND(K17*L17*revleg_mid,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_mid,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17)))</f>
         <v/>
       </c>
-      <c r="AV17" s="43">
+      <c r="AW17" s="43">
         <f>IF(((S17*pax_cap*load_full*ROUND(K17*L17*revleg_full,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_full,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17))&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/((S17*pax_cap*load_full*ROUND(K17*L17*revleg_full,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_full,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17)))</f>
         <v/>
       </c>
-      <c r="AW17" s="44" t="inlineStr">
-        <is>
-          <t>PREMIUM charter-divided tier: Hammamet/Nabeul bay per-seat excursion boat ~EUR 15-25 (3h marina cruise w/ swim stop) -&gt; ~EUR 20 x 1.08 ~= $22. Nearest premium per-seat water product on the bay.</t>
-        </is>
-      </c>
       <c r="AX17" s="44" t="n"/>
+      <c r="AY17" s="44" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
@@ -4732,15 +4800,25 @@
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
-          <t>Sfax → Sidi Youssef (Kerkennah Islands)</t>
+          <t>Yasmine Hammamet → Nabeul</t>
         </is>
       </c>
       <c r="D18" s="31" t="n">
-        <v>11</v>
-      </c>
-      <c r="E18" s="26" t="n"/>
-      <c r="F18" s="32" t="n"/>
-      <c r="G18" s="32" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="F18" s="32" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G18" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
       <c r="H18" s="19" t="n">
         <v>1</v>
       </c>
@@ -4840,9 +4918,7 @@
         <f>((D18*O18/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D18*O18*VLOOKUP(B18,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG18" s="31" t="n">
-        <v>1750000</v>
-      </c>
+      <c r="AG18" s="31" t="n"/>
       <c r="AH18" s="32" t="n"/>
       <c r="AI18" s="32" t="n"/>
       <c r="AJ18" s="39" t="n">
@@ -4853,7 +4929,7 @@
         <v/>
       </c>
       <c r="AL18" s="34">
-        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AS18="",9.9E+99,AS18),FLOOR(AK18/R18,1)))</f>
+        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AT18="",9.9E+99,AT18),FLOOR(AK18/R18,1)))</f>
         <v/>
       </c>
       <c r="AM18" s="38">
@@ -4861,7 +4937,7 @@
         <v/>
       </c>
       <c r="AN18" s="36">
-        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AS18="",9.9E+99,AS18),AK18/R18))</f>
+        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AT18="",9.9E+99,AT18),AK18/R18))</f>
         <v/>
       </c>
       <c r="AO18" s="38">
@@ -4869,23 +4945,32 @@
         <v/>
       </c>
       <c r="AP18" s="40" t="n"/>
-      <c r="AQ18" s="41" t="n"/>
+      <c r="AQ18" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR18" s="41" t="n"/>
-      <c r="AS18" s="42" t="n"/>
-      <c r="AT18" s="43">
+      <c r="AS18" s="41" t="n"/>
+      <c r="AT18" s="42" t="n"/>
+      <c r="AU18" s="43">
         <f>IF(((S18*pax_cap*load_thin*ROUND(K18*L18*revleg_thin,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_thin,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18))&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/((S18*pax_cap*load_thin*ROUND(K18*L18*revleg_thin,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_thin,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18)))</f>
         <v/>
       </c>
-      <c r="AU18" s="43">
+      <c r="AV18" s="43">
         <f>IF(((S18*pax_cap*load_mid*ROUND(K18*L18*revleg_mid,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_mid,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18))&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/((S18*pax_cap*load_mid*ROUND(K18*L18*revleg_mid,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_mid,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18)))</f>
         <v/>
       </c>
-      <c r="AV18" s="43">
+      <c r="AW18" s="43">
         <f>IF(((S18*pax_cap*load_full*ROUND(K18*L18*revleg_full,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_full,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18))&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/((S18*pax_cap*load_full*ROUND(K18*L18*revleg_full,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_full,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18)))</f>
         <v/>
       </c>
-      <c r="AW18" s="44" t="n"/>
-      <c r="AX18" s="44" t="n"/>
+      <c r="AX18" s="44" t="inlineStr">
+        <is>
+          <t>PREMIUM charter-divided tier: Hammamet/Nabeul bay per-seat excursion boat ~EUR 15-25 (3h marina cruise w/ swim stop) -&gt; ~EUR 20 x 1.08 ~= $22. Nearest premium per-seat water product on the bay.</t>
+        </is>
+      </c>
+      <c r="AY18" s="44" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
@@ -4900,25 +4985,15 @@
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>Sousse (Port El Kantaoui) → Monastir (Marina)</t>
+          <t>Sfax → Sidi Youssef (Kerkennah Islands)</t>
         </is>
       </c>
       <c r="D19" s="31" t="n">
-        <v>12</v>
-      </c>
-      <c r="E19" s="26" t="n">
-        <v>32</v>
-      </c>
-      <c r="F19" s="32" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="G19" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="32" t="n"/>
+      <c r="G19" s="32" t="n"/>
       <c r="H19" s="19" t="n">
         <v>1</v>
       </c>
@@ -4931,7 +5006,7 @@
         <v/>
       </c>
       <c r="K19" s="34">
-        <f>MIN(24,FLOOR(60*service_hr/J19,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J19,1))</f>
         <v/>
       </c>
       <c r="L19" s="34">
@@ -5019,7 +5094,7 @@
         <v/>
       </c>
       <c r="AG19" s="31" t="n">
-        <v>344000</v>
+        <v>1750000</v>
       </c>
       <c r="AH19" s="32" t="n"/>
       <c r="AI19" s="32" t="n"/>
@@ -5031,7 +5106,7 @@
         <v/>
       </c>
       <c r="AL19" s="34">
-        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AS19="",9.9E+99,AS19),FLOOR(AK19/R19,1)))</f>
+        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AT19="",9.9E+99,AT19),FLOOR(AK19/R19,1)))</f>
         <v/>
       </c>
       <c r="AM19" s="38">
@@ -5039,7 +5114,7 @@
         <v/>
       </c>
       <c r="AN19" s="36">
-        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AS19="",9.9E+99,AS19),AK19/R19))</f>
+        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AT19="",9.9E+99,AT19),AK19/R19))</f>
         <v/>
       </c>
       <c r="AO19" s="38">
@@ -5047,118 +5122,281 @@
         <v/>
       </c>
       <c r="AP19" s="40" t="n"/>
-      <c r="AQ19" s="41" t="n"/>
+      <c r="AQ19" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR19" s="41" t="n"/>
-      <c r="AS19" s="42" t="n"/>
-      <c r="AT19" s="43">
+      <c r="AS19" s="41" t="n"/>
+      <c r="AT19" s="42" t="n"/>
+      <c r="AU19" s="43">
         <f>IF(((S19*pax_cap*load_thin*ROUND(K19*L19*revleg_thin,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_thin,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19))&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/((S19*pax_cap*load_thin*ROUND(K19*L19*revleg_thin,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_thin,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19)))</f>
         <v/>
       </c>
-      <c r="AU19" s="43">
+      <c r="AV19" s="43">
         <f>IF(((S19*pax_cap*load_mid*ROUND(K19*L19*revleg_mid,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_mid,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19))&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/((S19*pax_cap*load_mid*ROUND(K19*L19*revleg_mid,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_mid,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19)))</f>
         <v/>
       </c>
-      <c r="AV19" s="43">
+      <c r="AW19" s="43">
         <f>IF(((S19*pax_cap*load_full*ROUND(K19*L19*revleg_full,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_full,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19))&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/((S19*pax_cap*load_full*ROUND(K19*L19*revleg_full,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_full,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19)))</f>
         <v/>
       </c>
-      <c r="AW19" s="44" t="inlineStr">
+      <c r="AX19" s="44" t="n"/>
+      <c r="AY19" s="44" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>Yassir Tunisia</t>
+        </is>
+      </c>
+      <c r="B20" s="29" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>Sousse (Port El Kantaoui) → Monastir (Marina)</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="F20" s="32" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G20" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="33">
+        <f>60*D20/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J20" s="33">
+        <f>I20+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K20" s="34">
+        <f>MIN(24,FLOOR(60*service_hr/J20,1))</f>
+        <v/>
+      </c>
+      <c r="L20" s="34">
+        <f>ROUND(365*mech_uptime*H20,0)</f>
+        <v/>
+      </c>
+      <c r="M20" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N20" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O20" s="34">
+        <f>ROUND(K20*L20*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P20" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q20" s="36">
+        <f>pax_cap*P20</f>
+        <v/>
+      </c>
+      <c r="R20" s="34">
+        <f>Q20*O20</f>
+        <v/>
+      </c>
+      <c r="S20" s="37">
+        <f>E20*discount</f>
+        <v/>
+      </c>
+      <c r="T20" s="38">
+        <f>S20*R20</f>
+        <v/>
+      </c>
+      <c r="U20" s="38">
+        <f>(battery/range_nm)*D20*O20*VLOOKUP(B20,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V20" s="38">
+        <f>VLOOKUP(B20,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W20" s="38">
+        <f>VLOOKUP(B20,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X20" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y20" s="38">
+        <f>VLOOKUP(B20,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z20" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA20" s="38">
+        <f>U20+V20+W20+X20+Y20+Z20</f>
+        <v/>
+      </c>
+      <c r="AB20" s="38">
+        <f>VLOOKUP(B20,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC20" s="38">
+        <f>T20-AA20</f>
+        <v/>
+      </c>
+      <c r="AD20" s="35">
+        <f>IF(T20=0,"",AC20/T20)</f>
+        <v/>
+      </c>
+      <c r="AE20" s="36">
+        <f>IF(AC20&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/AC20)</f>
+        <v/>
+      </c>
+      <c r="AF20" s="33">
+        <f>((D20*O20/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D20*O20*VLOOKUP(B20,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG20" s="31" t="n">
+        <v>344000</v>
+      </c>
+      <c r="AH20" s="32" t="n"/>
+      <c r="AI20" s="32" t="n"/>
+      <c r="AJ20" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK20" s="34">
+        <f>IF(AG20="","",AG20*AJ20)</f>
+        <v/>
+      </c>
+      <c r="AL20" s="34">
+        <f>IF(OR(AG20="",R20=0),"",MIN(IF(AT20="",9.9E+99,AT20),FLOOR(AK20/R20,1)))</f>
+        <v/>
+      </c>
+      <c r="AM20" s="38">
+        <f>IF(AL20="","",AL20*T20)</f>
+        <v/>
+      </c>
+      <c r="AN20" s="36">
+        <f>IF(OR(AG20="",R20=0),"",MIN(IF(AT20="",9.9E+99,AT20),AK20/R20))</f>
+        <v/>
+      </c>
+      <c r="AO20" s="38">
+        <f>IF(AN20="","",AN20*T20)</f>
+        <v/>
+      </c>
+      <c r="AP20" s="40" t="n"/>
+      <c r="AQ20" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AR20" s="41" t="n"/>
+      <c r="AS20" s="41" t="n"/>
+      <c r="AT20" s="42" t="n"/>
+      <c r="AU20" s="43">
+        <f>IF(((S20*pax_cap*load_thin*ROUND(K20*L20*revleg_thin,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_thin,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20))&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/((S20*pax_cap*load_thin*ROUND(K20*L20*revleg_thin,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_thin,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20)))</f>
+        <v/>
+      </c>
+      <c r="AV20" s="43">
+        <f>IF(((S20*pax_cap*load_mid*ROUND(K20*L20*revleg_mid,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_mid,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20))&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/((S20*pax_cap*load_mid*ROUND(K20*L20*revleg_mid,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_mid,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20)))</f>
+        <v/>
+      </c>
+      <c r="AW20" s="43">
+        <f>IF(((S20*pax_cap*load_full*ROUND(K20*L20*revleg_full,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_full,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20))&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/((S20*pax_cap*load_full*ROUND(K20*L20*revleg_full,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_full,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20)))</f>
+        <v/>
+      </c>
+      <c r="AX20" s="44" t="inlineStr">
         <is>
           <t>PREMIUM charter-divided tier: Port El Kantaoui per-seat catamaran / 'pirate boat' coastal cruise ~EUR 25-35 (Catamaran Amira day-cruise; half-day pirate-boat Sousse-Monastir) -&gt; midpoint ~EUR 30 x 1.08 ~= $32. This is the nearest premium per-seat water product operating on this exact coast.</t>
         </is>
       </c>
-      <c r="AX19" s="44" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="45" t="inlineStr">
+      <c r="AY20" s="44" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="45" t="inlineStr">
         <is>
           <t>TOTAL / median</t>
         </is>
       </c>
-      <c r="T20" s="46">
-        <f>SUM(T4:T19)</f>
-        <v/>
-      </c>
-      <c r="AC20" s="46">
-        <f>SUM(AC4:AC19)</f>
-        <v/>
-      </c>
-      <c r="AD20" s="47">
-        <f>IF(T20=0,"",AC20/T20)</f>
-        <v/>
-      </c>
-      <c r="AL20" s="48">
-        <f>SUM(AL4:AL19)</f>
-        <v/>
-      </c>
-      <c r="AM20" s="46">
-        <f>SUM(AM4:AM19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="T21" s="46">
+        <f>SUM(T4:T20)</f>
+        <v/>
+      </c>
+      <c r="AC21" s="46">
+        <f>SUM(AC4:AC20)</f>
+        <v/>
+      </c>
+      <c r="AD21" s="47">
+        <f>IF(T21=0,"",AC21/T21)</f>
+        <v/>
+      </c>
+      <c r="AL21" s="48">
+        <f>SUM(AL4:AL20)</f>
+        <v/>
+      </c>
+      <c r="AM21" s="46">
+        <f>SUM(AM4:AM20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Market fleet build-up — grounded floor (network-sum of raw vessel fractions per market, rounded once; subset slices excluded; legacy per-corridor-floor totals above kept for reference)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>Fleet basis</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>Raw vessels (sum)</t>
         </is>
       </c>
-      <c r="D23" s="24" t="inlineStr">
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>Fleet (rounded once)</t>
         </is>
       </c>
-      <c r="E23" s="24" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>Market rev/yr (raw sum)</t>
         </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="25" t="inlineStr">
-        <is>
-          <t>Yassir Algeria</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>aspirational</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D24" s="49">
-        <f>SUMIFS(AL4:AL19,A4:A19,"Yassir Algeria",AP4:AP19,"=",AQ4:AQ19,"=",AR4:AR19,"=")</f>
-        <v/>
-      </c>
-      <c r="E24" s="50">
-        <f>SUMIFS(AM4:AM19,A4:A19,"Yassir Algeria",AP4:AP19,"=",AQ4:AQ19,"=",AR4:AR19,"=")</f>
-        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t>Yassir Morocco</t>
+          <t>Yassir Algeria</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
@@ -5172,82 +5410,122 @@
         </is>
       </c>
       <c r="D25" s="49">
-        <f>SUMIFS(AL4:AL19,A4:A19,"Yassir Morocco",AP4:AP19,"=",AQ4:AQ19,"=",AR4:AR19,"=")</f>
+        <f>SUMIFS(AL4:AL20,A4:A20,"Yassir Algeria",AP4:AP20,"=",AQ4:AQ20,"Grounded")</f>
         <v/>
       </c>
       <c r="E25" s="50">
-        <f>SUMIFS(AM4:AM19,A4:A19,"Yassir Morocco",AP4:AP19,"=",AQ4:AQ19,"=",AR4:AR19,"=")</f>
+        <f>SUMIFS(AM4:AM20,A4:A20,"Yassir Algeria",AP4:AP20,"=",AQ4:AQ20,"Grounded")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="25" t="inlineStr">
         <is>
+          <t>Yassir Morocco</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>aspirational</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" s="49">
+        <f>SUMIFS(AL4:AL20,A4:A20,"Yassir Morocco",AP4:AP20,"=",AQ4:AQ20,"Grounded")</f>
+        <v/>
+      </c>
+      <c r="E26" s="50">
+        <f>SUMIFS(AM4:AM20,A4:A20,"Yassir Morocco",AP4:AP20,"=",AQ4:AQ20,"Grounded")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
           <t>Yassir Tunisia</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>aspirational</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D26" s="49">
-        <f>SUMIFS(AL4:AL19,A4:A19,"Yassir Tunisia",AP4:AP19,"=",AQ4:AQ19,"=",AR4:AR19,"=")</f>
-        <v/>
-      </c>
-      <c r="E26" s="50">
-        <f>SUMIFS(AM4:AM19,A4:A19,"Yassir Tunisia",AP4:AP19,"=",AQ4:AQ19,"=",AR4:AR19,"=")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="45" t="inlineStr">
+      <c r="D27" s="49">
+        <f>SUMIFS(AL4:AL20,A4:A20,"Yassir Tunisia",AP4:AP20,"=",AQ4:AQ20,"Grounded")</f>
+        <v/>
+      </c>
+      <c r="E27" s="50">
+        <f>SUMIFS(AM4:AM20,A4:A20,"Yassir Tunisia",AP4:AP20,"=",AQ4:AQ20,"Grounded")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="45" t="inlineStr">
         <is>
           <t>GROUNDED FLOOR (PUBLISHED)</t>
         </is>
       </c>
-      <c r="D27" s="48">
-        <f>SUM(D24:D26)</f>
-        <v/>
-      </c>
-      <c r="E27" s="46">
-        <f>SUM(E24:E26)</f>
+      <c r="D28" s="48">
+        <f>SUM(D25:D27)</f>
+        <v/>
+      </c>
+      <c r="E28" s="46">
+        <f>SUM(E25:E27)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="51" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>ESTIMATED DEMAND (country-median cascade; held OUT of grounded floor)</t>
+        </is>
+      </c>
+      <c r="D29" s="51">
+        <f>SUMIF(AQ4:AQ20,"Estimated",AL4:AL20)</f>
+        <v/>
+      </c>
+      <c r="E29" s="52">
+        <f>SUMIF(AQ4:AQ20,"Estimated",AM4:AM20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="53" t="inlineStr">
         <is>
           <t>Held for Quanta-LR (&gt;70nm, roadmap H2 2026+):</t>
         </is>
       </c>
-      <c r="C29" s="52" t="inlineStr">
+      <c r="C30" s="54" t="inlineStr">
         <is>
           <t>Tunis (La Goulette) → Palermo (Sicily, Italy) (170nm)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="C30" s="52" t="inlineStr">
+    <row r="31">
+      <c r="C31" s="54" t="inlineStr">
         <is>
           <t>Nador (Beni Ensar) → Almeria (Spain) (92nm)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="C31" s="52" t="inlineStr">
+    <row r="32">
+      <c r="C32" s="54" t="inlineStr">
         <is>
           <t>Port d'Oran → Mostaganem port (81.7nm)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="C32" s="52" t="inlineStr">
+    <row r="33">
+      <c r="C33" s="54" t="inlineStr">
         <is>
           <t>Port de Béjaïa → Port d'Alger (113.8nm)</t>
         </is>
@@ -5255,8 +5533,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A22:L22"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A23:L23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5479,7 +5757,7 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Live sum of grounded corridor market-rev (10% capture, today's demand, sourced corridors).</t>
+          <t>Live sum of grounded-floor corridor market-rev only (Floor bucket = Grounded; cascade-estimated rows held out). Matches growth.py _headline_anchor and deck TAM.</t>
         </is>
       </c>
     </row>
@@ -5668,12 +5946,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="53" t="inlineStr">
+      <c r="A26" s="55" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B26" s="54" t="inlineStr">
+      <c r="B26" s="56" t="inlineStr">
         <is>
           <t>All rungs are one multiplication chain off M_today, which is live off the corridor floor. Change any input (a fare, a multiplier, the scenario) and the whole ladder moves. Bands (low/MID/high) are never single points; greenfield census is per-partner.</t>
         </is>

--- a/finance/_refresh_yassir.xlsx
+++ b/finance/_refresh_yassir.xlsx
@@ -44,9 +44,9 @@
     <definedName name="scenario">'Assumptions'!$B$38</definedName>
     <definedName name="load_sel">'Assumptions'!$B$39</definedName>
     <definedName name="revleg_sel">'Assumptions'!$B$40</definedName>
-    <definedName name="country_opex">'Country opex'!$A$4:$G$6</definedName>
-    <definedName name="som_floor_fleet">'Corridor economics'!$D$28</definedName>
-    <definedName name="som_floor_rev">'Corridor economics'!$E$28</definedName>
+    <definedName name="country_opex">'Country opex'!$A$4:$G$7</definedName>
+    <definedName name="som_floor_fleet">'Corridor economics'!$D$33</definedName>
+    <definedName name="som_floor_rev">'Corridor economics'!$E$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1813,7 +1813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1938,28 +1938,58 @@
     <row r="6">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="C6" s="27" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="G6" s="26" t="n">
         <v>600000</v>
       </c>
       <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Modeled from national maritime-wage / cost-of-living index vs SG anchor | Modeled from national commercial electricity tariff avg | Modeled berth/marina overhead vs SG anchor by cost index | CAPEX LB-243 US/EU=$900K else $600K</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>600000</v>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>Modeled from national maritime-wage / cost-of-living index vs SG anchor | Modeled from national commercial electricity tariff avg | Modeled berth/marina overhead vs SG anchor by cost index | CAPEX LB-243 US/EU=$900K else $600K</t>
         </is>
@@ -1979,7 +2009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2316,7 +2346,7 @@
     <row r="4">
       <c r="A4" s="29" t="inlineStr">
         <is>
-          <t>Yassir Algeria</t>
+          <t>Yassir</t>
         </is>
       </c>
       <c r="B4" s="29" t="inlineStr">
@@ -2326,15 +2356,13 @@
       </c>
       <c r="C4" s="30" t="inlineStr">
         <is>
-          <t>La Pêcherie / Port d'Alger → El Djamila / Aïn Bénian</t>
+          <t>Port of Annaba (Môle Cigogne / Quai Nord) → Annaba Corniche — Plage Rizi Amor / Saint-Cloud</t>
         </is>
       </c>
       <c r="D4" s="31" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="E4" s="26" t="n">
-        <v>18</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="E4" s="26" t="n"/>
       <c r="F4" s="32" t="n"/>
       <c r="G4" s="32" t="n"/>
       <c r="H4" s="19" t="n">
@@ -2436,9 +2464,7 @@
         <f>((D4*O4/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D4*O4*VLOOKUP(B4,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG4" s="31" t="n">
-        <v>170280</v>
-      </c>
+      <c r="AG4" s="31" t="n"/>
       <c r="AH4" s="32" t="n"/>
       <c r="AI4" s="32" t="n"/>
       <c r="AJ4" s="39" t="n">
@@ -2467,7 +2493,7 @@
       <c r="AP4" s="40" t="n"/>
       <c r="AQ4" s="32" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Estimated</t>
         </is>
       </c>
       <c r="AR4" s="41" t="n"/>
@@ -2485,31 +2511,27 @@
         <f>IF(((S4*pax_cap*load_full*ROUND(K4*L4*revleg_full,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_full,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_full*ROUND(K4*L4*revleg_full,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_full,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AX4" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[LB-255 PREMIUM RE-FARE: subsidized comparable $3.7 lifted to premium on-demand floor $18.0] </t>
-        </is>
-      </c>
+      <c r="AX4" s="44" t="n"/>
       <c r="AY4" s="44" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="29" t="inlineStr">
         <is>
-          <t>Yassir Morocco</t>
+          <t>Yassir</t>
         </is>
       </c>
       <c r="B5" s="29" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C5" s="30" t="inlineStr">
         <is>
-          <t>Rabat → Sale</t>
+          <t>Gare Maritime / Port d'Oran → Ain El Turck / Kristel waterfront</t>
         </is>
       </c>
       <c r="D5" s="31" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="E5" s="26" t="n"/>
       <c r="F5" s="32" t="n"/>
@@ -2666,23 +2688,25 @@
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>Yassir Morocco</t>
+          <t>Yassir</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
         <is>
-          <t>Rabat → Sale</t>
+          <t>La Pêcherie / Port d'Alger → El Djamila / Aïn Bénian</t>
         </is>
       </c>
       <c r="D6" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E6" s="26" t="n"/>
+        <v>8.5</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>18</v>
+      </c>
       <c r="F6" s="32" t="n"/>
       <c r="G6" s="32" t="n"/>
       <c r="H6" s="19" t="n">
@@ -2697,7 +2721,7 @@
         <v/>
       </c>
       <c r="K6" s="34">
-        <f>MIN(24,FLOOR(60*service_hr/J6,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J6,1))</f>
         <v/>
       </c>
       <c r="L6" s="34">
@@ -2784,7 +2808,9 @@
         <f>((D6*O6/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D6*O6*VLOOKUP(B6,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG6" s="31" t="n"/>
+      <c r="AG6" s="31" t="n">
+        <v>170280</v>
+      </c>
       <c r="AH6" s="32" t="n"/>
       <c r="AI6" s="32" t="n"/>
       <c r="AJ6" s="39" t="n">
@@ -2813,7 +2839,7 @@
       <c r="AP6" s="40" t="n"/>
       <c r="AQ6" s="32" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="AR6" s="41" t="n"/>
@@ -2831,41 +2857,35 @@
         <f>IF(((S6*pax_cap*load_full*ROUND(K6*L6*revleg_full,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_full,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_full*ROUND(K6*L6*revleg_full,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_full,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AX6" s="44" t="n"/>
+      <c r="AX6" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[LB-255 PREMIUM RE-FARE: subsidized comparable $3.7 lifted to premium on-demand floor $18.0] </t>
+        </is>
+      </c>
       <c r="AY6" s="44" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
         <is>
-          <t>Yassir Morocco</t>
+          <t>Yassir</t>
         </is>
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C7" s="30" t="inlineStr">
         <is>
-          <t>Tangier Marina Bay → Tarifa (cross-strait excluded)</t>
+          <t>La Pêcherie / Port d'Alger / Gare Maritime → Tamentfoust (east bay harbour)</t>
         </is>
       </c>
       <c r="D7" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="F7" s="32" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="G7" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+        <v>10.3</v>
+      </c>
+      <c r="E7" s="26" t="n"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="32" t="n"/>
       <c r="H7" s="19" t="n">
         <v>1</v>
       </c>
@@ -2965,9 +2985,7 @@
         <f>((D7*O7/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D7*O7*VLOOKUP(B7,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG7" s="31" t="n">
-        <v>760778</v>
-      </c>
+      <c r="AG7" s="31" t="n"/>
       <c r="AH7" s="32" t="n"/>
       <c r="AI7" s="32" t="n"/>
       <c r="AJ7" s="39" t="n">
@@ -2996,7 +3014,7 @@
       <c r="AP7" s="40" t="n"/>
       <c r="AQ7" s="32" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Estimated</t>
         </is>
       </c>
       <c r="AR7" s="41" t="n"/>
@@ -3014,31 +3032,27 @@
         <f>IF(((S7*pax_cap*load_full*ROUND(K7*L7*revleg_full,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_full,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_full*ROUND(K7*L7*revleg_full,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_full,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AX7" s="44" t="inlineStr">
-        <is>
-          <t>PREMIUM tier: standard adult FOOT-PASSENGER one-way fast-ferry fare Tarifa&lt;-&gt;Tangier Ville ~EUR 40.25 (traveller-reported foot fare) x 1.08 = ~$43.5; DirectFerries lists 'from $46'. THIS is the Navier-modeled per-seat tier.</t>
-        </is>
-      </c>
+      <c r="AX7" s="44" t="n"/>
       <c r="AY7" s="44" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
         <is>
-          <t>Yassir Morocco</t>
+          <t>Yassir</t>
         </is>
       </c>
       <c r="B8" s="29" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C8" s="30" t="inlineStr">
         <is>
-          <t>Agadir Marina → Taghazout</t>
+          <t>Port de Sidi Fredj (marina) → El Djamila / Aïn Bénian</t>
         </is>
       </c>
       <c r="D8" s="31" t="n">
-        <v>9</v>
+        <v>13.8</v>
       </c>
       <c r="E8" s="26" t="n"/>
       <c r="F8" s="32" t="n"/>
@@ -3142,9 +3156,7 @@
         <f>((D8*O8/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D8*O8*VLOOKUP(B8,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG8" s="31" t="n">
-        <v>77500</v>
-      </c>
+      <c r="AG8" s="31" t="n"/>
       <c r="AH8" s="32" t="n"/>
       <c r="AI8" s="32" t="n"/>
       <c r="AJ8" s="39" t="n">
@@ -3197,7 +3209,7 @@
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
         <is>
-          <t>Yassir Morocco</t>
+          <t>Yassir</t>
         </is>
       </c>
       <c r="B9" s="29" t="inlineStr">
@@ -3207,11 +3219,11 @@
       </c>
       <c r="C9" s="30" t="inlineStr">
         <is>
-          <t>Casablanca → Mohammedia</t>
+          <t>Rabat → Sale</t>
         </is>
       </c>
       <c r="D9" s="31" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="E9" s="26" t="n"/>
       <c r="F9" s="32" t="n"/>
@@ -3228,7 +3240,7 @@
         <v/>
       </c>
       <c r="K9" s="34">
-        <f>MIN(24,FLOOR(60*service_hr/J9,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J9,1))</f>
         <v/>
       </c>
       <c r="L9" s="34">
@@ -3368,7 +3380,7 @@
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>Yassir Morocco</t>
+          <t>Yassir</t>
         </is>
       </c>
       <c r="B10" s="29" t="inlineStr">
@@ -3378,25 +3390,15 @@
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>Tanger Med (Ksar el Majaz) → Algeciras (Spain)</t>
+          <t>Rabat → Sale</t>
         </is>
       </c>
       <c r="D10" s="31" t="n">
-        <v>13</v>
-      </c>
-      <c r="E10" s="26" t="n">
-        <v>38</v>
-      </c>
-      <c r="F10" s="32" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="G10" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="32" t="n"/>
+      <c r="G10" s="32" t="n"/>
       <c r="H10" s="19" t="n">
         <v>1</v>
       </c>
@@ -3409,7 +3411,7 @@
         <v/>
       </c>
       <c r="K10" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J10,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J10,1))</f>
         <v/>
       </c>
       <c r="L10" s="34">
@@ -3496,9 +3498,7 @@
         <f>((D10*O10/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D10*O10*VLOOKUP(B10,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG10" s="31" t="n">
-        <v>1610211</v>
-      </c>
+      <c r="AG10" s="31" t="n"/>
       <c r="AH10" s="32" t="n"/>
       <c r="AI10" s="32" t="n"/>
       <c r="AJ10" s="39" t="n">
@@ -3527,7 +3527,7 @@
       <c r="AP10" s="40" t="n"/>
       <c r="AQ10" s="32" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Estimated</t>
         </is>
       </c>
       <c r="AR10" s="41" t="n"/>
@@ -3545,17 +3545,13 @@
         <f>IF(((S10*pax_cap*load_full*ROUND(K10*L10*revleg_full,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_full,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((S10*pax_cap*load_full*ROUND(K10*L10*revleg_full,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_full,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10)))</f>
         <v/>
       </c>
-      <c r="AX10" s="44" t="inlineStr">
-        <is>
-          <t>PREMIUM tier: standard adult FOOT-PASSENGER one-way Tanger Med&lt;-&gt;Algeciras ~EUR 35 x 1.08 = ~$38 (Strait fast-ferry foot fares cluster EUR 30-40).</t>
-        </is>
-      </c>
+      <c r="AX10" s="44" t="n"/>
       <c r="AY10" s="44" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
         <is>
-          <t>Yassir Morocco</t>
+          <t>Yassir</t>
         </is>
       </c>
       <c r="B11" s="29" t="inlineStr">
@@ -3565,15 +3561,25 @@
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>Al Hoceima → Cala Iris</t>
+          <t>Tangier Marina Bay → Tarifa (cross-strait excluded)</t>
         </is>
       </c>
       <c r="D11" s="31" t="n">
-        <v>16</v>
-      </c>
-      <c r="E11" s="26" t="n"/>
-      <c r="F11" s="32" t="n"/>
-      <c r="G11" s="32" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G11" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
       <c r="H11" s="19" t="n">
         <v>1</v>
       </c>
@@ -3586,7 +3592,7 @@
         <v/>
       </c>
       <c r="K11" s="34">
-        <f>MIN(24,FLOOR(60*service_hr/J11,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J11,1))</f>
         <v/>
       </c>
       <c r="L11" s="34">
@@ -3673,7 +3679,9 @@
         <f>((D11*O11/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D11*O11*VLOOKUP(B11,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG11" s="31" t="n"/>
+      <c r="AG11" s="31" t="n">
+        <v>760778</v>
+      </c>
       <c r="AH11" s="32" t="n"/>
       <c r="AI11" s="32" t="n"/>
       <c r="AJ11" s="39" t="n">
@@ -3702,7 +3710,7 @@
       <c r="AP11" s="40" t="n"/>
       <c r="AQ11" s="32" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="AR11" s="41" t="n"/>
@@ -3720,13 +3728,17 @@
         <f>IF(((S11*pax_cap*load_full*ROUND(K11*L11*revleg_full,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_full,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((S11*pax_cap*load_full*ROUND(K11*L11*revleg_full,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_full,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11)))</f>
         <v/>
       </c>
-      <c r="AX11" s="44" t="n"/>
+      <c r="AX11" s="44" t="inlineStr">
+        <is>
+          <t>PREMIUM tier: standard adult FOOT-PASSENGER one-way fast-ferry fare Tarifa&lt;-&gt;Tangier Ville ~EUR 40.25 (traveller-reported foot fare) x 1.08 = ~$43.5; DirectFerries lists 'from $46'. THIS is the Navier-modeled per-seat tier.</t>
+        </is>
+      </c>
       <c r="AY11" s="44" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="29" t="inlineStr">
         <is>
-          <t>Yassir Morocco</t>
+          <t>Yassir</t>
         </is>
       </c>
       <c r="B12" s="29" t="inlineStr">
@@ -3736,25 +3748,15 @@
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>Tanger Med → Ceuta (Spanish enclave)</t>
+          <t>Agadir Marina → Taghazout</t>
         </is>
       </c>
       <c r="D12" s="31" t="n">
-        <v>22</v>
-      </c>
-      <c r="E12" s="26" t="n">
-        <v>36</v>
-      </c>
-      <c r="F12" s="32" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="G12" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="32" t="n"/>
       <c r="H12" s="19" t="n">
         <v>1</v>
       </c>
@@ -3854,7 +3856,9 @@
         <f>((D12*O12/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D12*O12*VLOOKUP(B12,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG12" s="31" t="n"/>
+      <c r="AG12" s="31" t="n">
+        <v>77500</v>
+      </c>
       <c r="AH12" s="32" t="n"/>
       <c r="AI12" s="32" t="n"/>
       <c r="AJ12" s="39" t="n">
@@ -3883,7 +3887,7 @@
       <c r="AP12" s="40" t="n"/>
       <c r="AQ12" s="32" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="AR12" s="41" t="n"/>
@@ -3901,17 +3905,13 @@
         <f>IF(((S12*pax_cap*load_full*ROUND(K12*L12*revleg_full,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_full,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((S12*pax_cap*load_full*ROUND(K12*L12*revleg_full,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_full,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12)))</f>
         <v/>
       </c>
-      <c r="AX12" s="44" t="inlineStr">
-        <is>
-          <t>PREMIUM tier (nearest comparable = Algeciras&lt;-&gt;Ceuta fast ferry): avg foot-passenger fare ~EUR 33 x 1.08 ~= $36 (one-way ~EUR 25-35), 60 min fast ferry.</t>
-        </is>
-      </c>
+      <c r="AX12" s="44" t="n"/>
       <c r="AY12" s="44" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="29" t="inlineStr">
         <is>
-          <t>Yassir Morocco</t>
+          <t>Yassir</t>
         </is>
       </c>
       <c r="B13" s="29" t="inlineStr">
@@ -3921,11 +3921,11 @@
       </c>
       <c r="C13" s="30" t="inlineStr">
         <is>
-          <t>Casablanca → Rabat</t>
+          <t>Casablanca → Mohammedia</t>
         </is>
       </c>
       <c r="D13" s="31" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="E13" s="26" t="n"/>
       <c r="F13" s="32" t="n"/>
@@ -4029,9 +4029,7 @@
         <f>((D13*O13/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D13*O13*VLOOKUP(B13,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG13" s="31" t="n">
-        <v>165000</v>
-      </c>
+      <c r="AG13" s="31" t="n"/>
       <c r="AH13" s="32" t="n"/>
       <c r="AI13" s="32" t="n"/>
       <c r="AJ13" s="39" t="n">
@@ -4084,21 +4082,21 @@
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>Yassir Tunisia</t>
+          <t>Yassir</t>
         </is>
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
-          <t>Jorf (mainland) → Ajim (Djerba Island)</t>
+          <t>Al Hoceima → Cala Iris</t>
         </is>
       </c>
       <c r="D14" s="31" t="n">
-        <v>1.1</v>
+        <v>16</v>
       </c>
       <c r="E14" s="26" t="n"/>
       <c r="F14" s="32" t="n"/>
@@ -4115,7 +4113,7 @@
         <v/>
       </c>
       <c r="K14" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J14,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J14,1))</f>
         <v/>
       </c>
       <c r="L14" s="34">
@@ -4202,9 +4200,7 @@
         <f>((D14*O14/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D14*O14*VLOOKUP(B14,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG14" s="31" t="n">
-        <v>2463750</v>
-      </c>
+      <c r="AG14" s="31" t="n"/>
       <c r="AH14" s="32" t="n"/>
       <c r="AI14" s="32" t="n"/>
       <c r="AJ14" s="39" t="n">
@@ -4257,24 +4253,24 @@
     <row r="15">
       <c r="A15" s="29" t="inlineStr">
         <is>
-          <t>Yassir Tunisia</t>
+          <t>Yassir</t>
         </is>
       </c>
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>La Goulette → Sidi Bou Said</t>
+          <t>Tanger Med → Ceuta (Spanish enclave)</t>
         </is>
       </c>
       <c r="D15" s="31" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F15" s="32" t="inlineStr">
         <is>
@@ -4385,9 +4381,7 @@
         <f>((D15*O15/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D15*O15*VLOOKUP(B15,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG15" s="31" t="n">
-        <v>222000</v>
-      </c>
+      <c r="AG15" s="31" t="n"/>
       <c r="AH15" s="32" t="n"/>
       <c r="AI15" s="32" t="n"/>
       <c r="AJ15" s="39" t="n">
@@ -4416,7 +4410,7 @@
       <c r="AP15" s="40" t="n"/>
       <c r="AQ15" s="32" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Estimated</t>
         </is>
       </c>
       <c r="AR15" s="41" t="n"/>
@@ -4436,7 +4430,7 @@
       </c>
       <c r="AX15" s="44" t="inlineStr">
         <is>
-          <t>PREMIUM charter-divided tier: Gulf of Tunis / Sidi Bou Said per-seat excursion cruise ~EUR 25 (pirate-boat dinner cruise 'from EUR 30'; 3h marina cruise EUR 15-20) x 1.08 ~= $27. Nearest premium per-seat water product on this corridor; no scheduled fast catamaran exists.</t>
+          <t>PREMIUM tier (nearest comparable = Algeciras&lt;-&gt;Ceuta fast ferry): avg foot-passenger fare ~EUR 33 x 1.08 ~= $36 (one-way ~EUR 25-35), 60 min fast ferry.</t>
         </is>
       </c>
       <c r="AY15" s="44" t="n"/>
@@ -4444,21 +4438,21 @@
     <row r="16">
       <c r="A16" s="29" t="inlineStr">
         <is>
-          <t>Yassir Tunisia</t>
+          <t>Yassir</t>
         </is>
       </c>
       <c r="B16" s="29" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C16" s="30" t="inlineStr">
         <is>
-          <t>Tunis (Tunis Marine) → La Goulette</t>
+          <t>Casablanca → Rabat</t>
         </is>
       </c>
       <c r="D16" s="31" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="E16" s="26" t="n"/>
       <c r="F16" s="32" t="n"/>
@@ -4563,7 +4557,7 @@
         <v/>
       </c>
       <c r="AG16" s="31" t="n">
-        <v>296000</v>
+        <v>165000</v>
       </c>
       <c r="AH16" s="32" t="n"/>
       <c r="AI16" s="32" t="n"/>
@@ -4593,7 +4587,7 @@
       <c r="AP16" s="40" t="n"/>
       <c r="AQ16" s="32" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="AR16" s="41" t="n"/>
@@ -4617,25 +4611,35 @@
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>Yassir Tunisia</t>
+          <t>Yassir</t>
         </is>
       </c>
       <c r="B17" s="29" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>Tunis (La Goulette) → La Marsa / Gammarth</t>
+          <t>Dakar (Plage de Ngor) → Ile de Ngor</t>
         </is>
       </c>
       <c r="D17" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="E17" s="26" t="n"/>
-      <c r="F17" s="32" t="n"/>
-      <c r="G17" s="32" t="n"/>
+        <v>0.3</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G17" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
       <c r="H17" s="19" t="n">
         <v>1</v>
       </c>
@@ -4648,7 +4652,7 @@
         <v/>
       </c>
       <c r="K17" s="34">
-        <f>MIN(24,FLOOR(60*service_hr/J17,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J17,1))</f>
         <v/>
       </c>
       <c r="L17" s="34">
@@ -4735,9 +4739,7 @@
         <f>((D17*O17/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D17*O17*VLOOKUP(B17,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG17" s="31" t="n">
-        <v>222000</v>
-      </c>
+      <c r="AG17" s="31" t="n"/>
       <c r="AH17" s="32" t="n"/>
       <c r="AI17" s="32" t="n"/>
       <c r="AJ17" s="39" t="n">
@@ -4784,30 +4786,34 @@
         <f>IF(((S17*pax_cap*load_full*ROUND(K17*L17*revleg_full,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_full,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17))&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/((S17*pax_cap*load_full*ROUND(K17*L17*revleg_full,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_full,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17)))</f>
         <v/>
       </c>
-      <c r="AX17" s="44" t="n"/>
+      <c r="AX17" s="44" t="inlineStr">
+        <is>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $0.87 lifted to premium on-demand floor $18.0] Pirogue shuttle 1,000 FCFA ALLER-RETOUR =&gt; ~500 one-way =&gt; $0.87. NOTE: this corridor has essentially no premium tier today (single low fare); $0.87 doubles as both anchor and floor.</t>
+        </is>
+      </c>
       <c r="AY17" s="44" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>Yassir Tunisia</t>
+          <t>Yassir</t>
         </is>
       </c>
       <c r="B18" s="29" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
-          <t>Yasmine Hammamet → Nabeul</t>
+          <t>Dakar (Soumbedioune / Mole) → Parc National des Iles de la Madeleine (Ile aux Serpents/Sarpan)</t>
         </is>
       </c>
       <c r="D18" s="31" t="n">
-        <v>7</v>
+        <v>2.2</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F18" s="32" t="inlineStr">
         <is>
@@ -4967,7 +4973,7 @@
       </c>
       <c r="AX18" s="44" t="inlineStr">
         <is>
-          <t>PREMIUM charter-divided tier: Hammamet/Nabeul bay per-seat excursion boat ~EUR 15-25 (3h marina cruise w/ swim stop) -&gt; ~EUR 20 x 1.08 ~= $22. Nearest premium per-seat water product on the bay.</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.48 lifted to premium on-demand floor $18.0] Divided-pirogue per-seat: 4,000 FCFA/pers ALLER-RETOUR for the crossing (excl. 1,000 FCFA park entry + 5,000 FCFA/group guide) =&gt; ~2,000 one-way =&gt; $3.48.</t>
         </is>
       </c>
       <c r="AY18" s="44" t="n"/>
@@ -4975,25 +4981,35 @@
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>Yassir Tunisia</t>
+          <t>Yassir</t>
         </is>
       </c>
       <c r="B19" s="29" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>Sfax → Sidi Youssef (Kerkennah Islands)</t>
+          <t>Dakar Port → Île de Gorée</t>
         </is>
       </c>
       <c r="D19" s="31" t="n">
-        <v>11</v>
-      </c>
-      <c r="E19" s="26" t="n"/>
-      <c r="F19" s="32" t="n"/>
-      <c r="G19" s="32" t="n"/>
+        <v>2.5</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="F19" s="32" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G19" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
       <c r="H19" s="19" t="n">
         <v>1</v>
       </c>
@@ -5094,12 +5110,16 @@
         <v/>
       </c>
       <c r="AG19" s="31" t="n">
-        <v>1750000</v>
+        <v>80000</v>
       </c>
       <c r="AH19" s="32" t="n"/>
-      <c r="AI19" s="32" t="n"/>
+      <c r="AI19" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
       <c r="AJ19" s="39" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="AK19" s="34">
         <f>IF(AG19="","",AG19*AJ19)</f>
@@ -5124,7 +5144,7 @@
       <c r="AP19" s="40" t="n"/>
       <c r="AQ19" s="32" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="AR19" s="41" t="n"/>
@@ -5142,41 +5162,35 @@
         <f>IF(((S19*pax_cap*load_full*ROUND(K19*L19*revleg_full,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_full,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19))&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/((S19*pax_cap*load_full*ROUND(K19*L19*revleg_full,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_full,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19)))</f>
         <v/>
       </c>
-      <c r="AX19" s="44" t="n"/>
+      <c r="AX19" s="44" t="inlineStr">
+        <is>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.22 lifted to premium on-demand floor $18.0] PREMIUM tier: non-resident (foreign) adult tourist fare 6,000 FCFA ALLER-RETOUR (effective Oct 2025) =&gt; ~3,000 FCFA one-way =&gt; $5.22. (Pre-Oct-2025 non-resident fare was 5,200 FCFA RT.)</t>
+        </is>
+      </c>
       <c r="AY19" s="44" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="29" t="inlineStr">
         <is>
-          <t>Yassir Tunisia</t>
+          <t>Yassir</t>
         </is>
       </c>
       <c r="B20" s="29" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C20" s="30" t="inlineStr">
         <is>
-          <t>Sousse (Port El Kantaoui) → Monastir (Marina)</t>
+          <t>Dakar (Yoff / Almadies) → Dakar (Soumbedioune / Plateau)</t>
         </is>
       </c>
       <c r="D20" s="31" t="n">
-        <v>12</v>
-      </c>
-      <c r="E20" s="26" t="n">
-        <v>32</v>
-      </c>
-      <c r="F20" s="32" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="G20" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E20" s="26" t="n"/>
+      <c r="F20" s="32" t="n"/>
+      <c r="G20" s="32" t="n"/>
       <c r="H20" s="19" t="n">
         <v>1</v>
       </c>
@@ -5189,7 +5203,7 @@
         <v/>
       </c>
       <c r="K20" s="34">
-        <f>MIN(24,FLOOR(60*service_hr/J20,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J20,1))</f>
         <v/>
       </c>
       <c r="L20" s="34">
@@ -5276,9 +5290,7 @@
         <f>((D20*O20/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D20*O20*VLOOKUP(B20,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG20" s="31" t="n">
-        <v>344000</v>
-      </c>
+      <c r="AG20" s="31" t="n"/>
       <c r="AH20" s="32" t="n"/>
       <c r="AI20" s="32" t="n"/>
       <c r="AJ20" s="39" t="n">
@@ -5307,7 +5319,7 @@
       <c r="AP20" s="40" t="n"/>
       <c r="AQ20" s="32" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Estimated</t>
         </is>
       </c>
       <c r="AR20" s="41" t="n"/>
@@ -5325,216 +5337,1412 @@
         <f>IF(((S20*pax_cap*load_full*ROUND(K20*L20*revleg_full,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_full,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20))&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/((S20*pax_cap*load_full*ROUND(K20*L20*revleg_full,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_full,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20)))</f>
         <v/>
       </c>
-      <c r="AX20" s="44" t="inlineStr">
+      <c r="AX20" s="44" t="n"/>
+      <c r="AY20" s="44" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>Yassir</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>Dakar / Mbour-Petite Cote → Foundiougne (Sine-Saloum delta)</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="E21" s="26" t="n"/>
+      <c r="F21" s="32" t="n"/>
+      <c r="G21" s="32" t="n"/>
+      <c r="H21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="33">
+        <f>60*D21/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J21" s="33">
+        <f>I21+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K21" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J21,1))</f>
+        <v/>
+      </c>
+      <c r="L21" s="34">
+        <f>ROUND(365*mech_uptime*H21,0)</f>
+        <v/>
+      </c>
+      <c r="M21" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N21" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O21" s="34">
+        <f>ROUND(K21*L21*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P21" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q21" s="36">
+        <f>pax_cap*P21</f>
+        <v/>
+      </c>
+      <c r="R21" s="34">
+        <f>Q21*O21</f>
+        <v/>
+      </c>
+      <c r="S21" s="37">
+        <f>E21*discount</f>
+        <v/>
+      </c>
+      <c r="T21" s="38">
+        <f>S21*R21</f>
+        <v/>
+      </c>
+      <c r="U21" s="38">
+        <f>(battery/range_nm)*D21*O21*VLOOKUP(B21,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V21" s="38">
+        <f>VLOOKUP(B21,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W21" s="38">
+        <f>VLOOKUP(B21,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X21" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y21" s="38">
+        <f>VLOOKUP(B21,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z21" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA21" s="38">
+        <f>U21+V21+W21+X21+Y21+Z21</f>
+        <v/>
+      </c>
+      <c r="AB21" s="38">
+        <f>VLOOKUP(B21,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC21" s="38">
+        <f>T21-AA21</f>
+        <v/>
+      </c>
+      <c r="AD21" s="35">
+        <f>IF(T21=0,"",AC21/T21)</f>
+        <v/>
+      </c>
+      <c r="AE21" s="36">
+        <f>IF(AC21&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/AC21)</f>
+        <v/>
+      </c>
+      <c r="AF21" s="33">
+        <f>((D21*O21/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D21*O21*VLOOKUP(B21,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG21" s="31" t="n"/>
+      <c r="AH21" s="32" t="n"/>
+      <c r="AI21" s="32" t="n"/>
+      <c r="AJ21" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK21" s="34">
+        <f>IF(AG21="","",AG21*AJ21)</f>
+        <v/>
+      </c>
+      <c r="AL21" s="34">
+        <f>IF(OR(AG21="",R21=0),"",MIN(IF(AT21="",9.9E+99,AT21),FLOOR(AK21/R21,1)))</f>
+        <v/>
+      </c>
+      <c r="AM21" s="38">
+        <f>IF(AL21="","",AL21*T21)</f>
+        <v/>
+      </c>
+      <c r="AN21" s="36">
+        <f>IF(OR(AG21="",R21=0),"",MIN(IF(AT21="",9.9E+99,AT21),AK21/R21))</f>
+        <v/>
+      </c>
+      <c r="AO21" s="38">
+        <f>IF(AN21="","",AN21*T21)</f>
+        <v/>
+      </c>
+      <c r="AP21" s="40" t="n"/>
+      <c r="AQ21" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="AR21" s="41" t="n"/>
+      <c r="AS21" s="41" t="n"/>
+      <c r="AT21" s="42" t="n"/>
+      <c r="AU21" s="43">
+        <f>IF(((S21*pax_cap*load_thin*ROUND(K21*L21*revleg_thin,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_thin,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21))&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/((S21*pax_cap*load_thin*ROUND(K21*L21*revleg_thin,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_thin,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21)))</f>
+        <v/>
+      </c>
+      <c r="AV21" s="43">
+        <f>IF(((S21*pax_cap*load_mid*ROUND(K21*L21*revleg_mid,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_mid,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21))&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/((S21*pax_cap*load_mid*ROUND(K21*L21*revleg_mid,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_mid,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21)))</f>
+        <v/>
+      </c>
+      <c r="AW21" s="43">
+        <f>IF(((S21*pax_cap*load_full*ROUND(K21*L21*revleg_full,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_full,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21))&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/((S21*pax_cap*load_full*ROUND(K21*L21*revleg_full,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_full,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21)))</f>
+        <v/>
+      </c>
+      <c r="AX21" s="44" t="n"/>
+      <c r="AY21" s="44" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>Yassir</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="C22" s="30" t="inlineStr">
+        <is>
+          <t>Jorf (mainland) → Ajim (Djerba Island)</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E22" s="26" t="n"/>
+      <c r="F22" s="32" t="n"/>
+      <c r="G22" s="32" t="n"/>
+      <c r="H22" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="33">
+        <f>60*D22/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J22" s="33">
+        <f>I22+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K22" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J22,1))</f>
+        <v/>
+      </c>
+      <c r="L22" s="34">
+        <f>ROUND(365*mech_uptime*H22,0)</f>
+        <v/>
+      </c>
+      <c r="M22" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N22" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O22" s="34">
+        <f>ROUND(K22*L22*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P22" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q22" s="36">
+        <f>pax_cap*P22</f>
+        <v/>
+      </c>
+      <c r="R22" s="34">
+        <f>Q22*O22</f>
+        <v/>
+      </c>
+      <c r="S22" s="37">
+        <f>E22*discount</f>
+        <v/>
+      </c>
+      <c r="T22" s="38">
+        <f>S22*R22</f>
+        <v/>
+      </c>
+      <c r="U22" s="38">
+        <f>(battery/range_nm)*D22*O22*VLOOKUP(B22,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V22" s="38">
+        <f>VLOOKUP(B22,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W22" s="38">
+        <f>VLOOKUP(B22,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X22" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y22" s="38">
+        <f>VLOOKUP(B22,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z22" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA22" s="38">
+        <f>U22+V22+W22+X22+Y22+Z22</f>
+        <v/>
+      </c>
+      <c r="AB22" s="38">
+        <f>VLOOKUP(B22,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC22" s="38">
+        <f>T22-AA22</f>
+        <v/>
+      </c>
+      <c r="AD22" s="35">
+        <f>IF(T22=0,"",AC22/T22)</f>
+        <v/>
+      </c>
+      <c r="AE22" s="36">
+        <f>IF(AC22&lt;=0,"",VLOOKUP(B22,country_opex,7,FALSE)/AC22)</f>
+        <v/>
+      </c>
+      <c r="AF22" s="33">
+        <f>((D22*O22/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D22*O22*VLOOKUP(B22,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG22" s="31" t="n">
+        <v>2463750</v>
+      </c>
+      <c r="AH22" s="32" t="n"/>
+      <c r="AI22" s="32" t="n"/>
+      <c r="AJ22" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK22" s="34">
+        <f>IF(AG22="","",AG22*AJ22)</f>
+        <v/>
+      </c>
+      <c r="AL22" s="34">
+        <f>IF(OR(AG22="",R22=0),"",MIN(IF(AT22="",9.9E+99,AT22),FLOOR(AK22/R22,1)))</f>
+        <v/>
+      </c>
+      <c r="AM22" s="38">
+        <f>IF(AL22="","",AL22*T22)</f>
+        <v/>
+      </c>
+      <c r="AN22" s="36">
+        <f>IF(OR(AG22="",R22=0),"",MIN(IF(AT22="",9.9E+99,AT22),AK22/R22))</f>
+        <v/>
+      </c>
+      <c r="AO22" s="38">
+        <f>IF(AN22="","",AN22*T22)</f>
+        <v/>
+      </c>
+      <c r="AP22" s="40" t="n"/>
+      <c r="AQ22" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AR22" s="41" t="n"/>
+      <c r="AS22" s="41" t="n"/>
+      <c r="AT22" s="42" t="n"/>
+      <c r="AU22" s="43">
+        <f>IF(((S22*pax_cap*load_thin*ROUND(K22*L22*revleg_thin,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_thin,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22))&lt;=0,"",VLOOKUP(B22,country_opex,7,FALSE)/((S22*pax_cap*load_thin*ROUND(K22*L22*revleg_thin,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_thin,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22)))</f>
+        <v/>
+      </c>
+      <c r="AV22" s="43">
+        <f>IF(((S22*pax_cap*load_mid*ROUND(K22*L22*revleg_mid,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_mid,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22))&lt;=0,"",VLOOKUP(B22,country_opex,7,FALSE)/((S22*pax_cap*load_mid*ROUND(K22*L22*revleg_mid,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_mid,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22)))</f>
+        <v/>
+      </c>
+      <c r="AW22" s="43">
+        <f>IF(((S22*pax_cap*load_full*ROUND(K22*L22*revleg_full,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_full,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22))&lt;=0,"",VLOOKUP(B22,country_opex,7,FALSE)/((S22*pax_cap*load_full*ROUND(K22*L22*revleg_full,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_full,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22)))</f>
+        <v/>
+      </c>
+      <c r="AX22" s="44" t="n"/>
+      <c r="AY22" s="44" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>Yassir</t>
+        </is>
+      </c>
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="C23" s="30" t="inlineStr">
+        <is>
+          <t>La Goulette → Sidi Bou Said</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>27</v>
+      </c>
+      <c r="F23" s="32" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G23" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="33">
+        <f>60*D23/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J23" s="33">
+        <f>I23+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K23" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J23,1))</f>
+        <v/>
+      </c>
+      <c r="L23" s="34">
+        <f>ROUND(365*mech_uptime*H23,0)</f>
+        <v/>
+      </c>
+      <c r="M23" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N23" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O23" s="34">
+        <f>ROUND(K23*L23*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P23" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q23" s="36">
+        <f>pax_cap*P23</f>
+        <v/>
+      </c>
+      <c r="R23" s="34">
+        <f>Q23*O23</f>
+        <v/>
+      </c>
+      <c r="S23" s="37">
+        <f>E23*discount</f>
+        <v/>
+      </c>
+      <c r="T23" s="38">
+        <f>S23*R23</f>
+        <v/>
+      </c>
+      <c r="U23" s="38">
+        <f>(battery/range_nm)*D23*O23*VLOOKUP(B23,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V23" s="38">
+        <f>VLOOKUP(B23,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W23" s="38">
+        <f>VLOOKUP(B23,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X23" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y23" s="38">
+        <f>VLOOKUP(B23,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z23" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA23" s="38">
+        <f>U23+V23+W23+X23+Y23+Z23</f>
+        <v/>
+      </c>
+      <c r="AB23" s="38">
+        <f>VLOOKUP(B23,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC23" s="38">
+        <f>T23-AA23</f>
+        <v/>
+      </c>
+      <c r="AD23" s="35">
+        <f>IF(T23=0,"",AC23/T23)</f>
+        <v/>
+      </c>
+      <c r="AE23" s="36">
+        <f>IF(AC23&lt;=0,"",VLOOKUP(B23,country_opex,7,FALSE)/AC23)</f>
+        <v/>
+      </c>
+      <c r="AF23" s="33">
+        <f>((D23*O23/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D23*O23*VLOOKUP(B23,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG23" s="31" t="n">
+        <v>222000</v>
+      </c>
+      <c r="AH23" s="32" t="n"/>
+      <c r="AI23" s="32" t="n"/>
+      <c r="AJ23" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK23" s="34">
+        <f>IF(AG23="","",AG23*AJ23)</f>
+        <v/>
+      </c>
+      <c r="AL23" s="34">
+        <f>IF(OR(AG23="",R23=0),"",MIN(IF(AT23="",9.9E+99,AT23),FLOOR(AK23/R23,1)))</f>
+        <v/>
+      </c>
+      <c r="AM23" s="38">
+        <f>IF(AL23="","",AL23*T23)</f>
+        <v/>
+      </c>
+      <c r="AN23" s="36">
+        <f>IF(OR(AG23="",R23=0),"",MIN(IF(AT23="",9.9E+99,AT23),AK23/R23))</f>
+        <v/>
+      </c>
+      <c r="AO23" s="38">
+        <f>IF(AN23="","",AN23*T23)</f>
+        <v/>
+      </c>
+      <c r="AP23" s="40" t="n"/>
+      <c r="AQ23" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AR23" s="41" t="n"/>
+      <c r="AS23" s="41" t="n"/>
+      <c r="AT23" s="42" t="n"/>
+      <c r="AU23" s="43">
+        <f>IF(((S23*pax_cap*load_thin*ROUND(K23*L23*revleg_thin,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_thin,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23))&lt;=0,"",VLOOKUP(B23,country_opex,7,FALSE)/((S23*pax_cap*load_thin*ROUND(K23*L23*revleg_thin,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_thin,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23)))</f>
+        <v/>
+      </c>
+      <c r="AV23" s="43">
+        <f>IF(((S23*pax_cap*load_mid*ROUND(K23*L23*revleg_mid,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_mid,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23))&lt;=0,"",VLOOKUP(B23,country_opex,7,FALSE)/((S23*pax_cap*load_mid*ROUND(K23*L23*revleg_mid,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_mid,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23)))</f>
+        <v/>
+      </c>
+      <c r="AW23" s="43">
+        <f>IF(((S23*pax_cap*load_full*ROUND(K23*L23*revleg_full,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_full,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23))&lt;=0,"",VLOOKUP(B23,country_opex,7,FALSE)/((S23*pax_cap*load_full*ROUND(K23*L23*revleg_full,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_full,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23)))</f>
+        <v/>
+      </c>
+      <c r="AX23" s="44" t="inlineStr">
+        <is>
+          <t>PREMIUM charter-divided tier: Gulf of Tunis / Sidi Bou Said per-seat excursion cruise ~EUR 25 (pirate-boat dinner cruise 'from EUR 30'; 3h marina cruise EUR 15-20) x 1.08 ~= $27. Nearest premium per-seat water product on this corridor; no scheduled fast catamaran exists.</t>
+        </is>
+      </c>
+      <c r="AY23" s="44" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>Yassir</t>
+        </is>
+      </c>
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="C24" s="30" t="inlineStr">
+        <is>
+          <t>Tunis (Tunis Marine) → La Goulette</t>
+        </is>
+      </c>
+      <c r="D24" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" s="26" t="n"/>
+      <c r="F24" s="32" t="n"/>
+      <c r="G24" s="32" t="n"/>
+      <c r="H24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="33">
+        <f>60*D24/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J24" s="33">
+        <f>I24+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K24" s="34">
+        <f>MIN(24,FLOOR(60*service_hr/J24,1))</f>
+        <v/>
+      </c>
+      <c r="L24" s="34">
+        <f>ROUND(365*mech_uptime*H24,0)</f>
+        <v/>
+      </c>
+      <c r="M24" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N24" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O24" s="34">
+        <f>ROUND(K24*L24*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P24" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q24" s="36">
+        <f>pax_cap*P24</f>
+        <v/>
+      </c>
+      <c r="R24" s="34">
+        <f>Q24*O24</f>
+        <v/>
+      </c>
+      <c r="S24" s="37">
+        <f>E24*discount</f>
+        <v/>
+      </c>
+      <c r="T24" s="38">
+        <f>S24*R24</f>
+        <v/>
+      </c>
+      <c r="U24" s="38">
+        <f>(battery/range_nm)*D24*O24*VLOOKUP(B24,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V24" s="38">
+        <f>VLOOKUP(B24,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W24" s="38">
+        <f>VLOOKUP(B24,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X24" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y24" s="38">
+        <f>VLOOKUP(B24,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z24" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA24" s="38">
+        <f>U24+V24+W24+X24+Y24+Z24</f>
+        <v/>
+      </c>
+      <c r="AB24" s="38">
+        <f>VLOOKUP(B24,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC24" s="38">
+        <f>T24-AA24</f>
+        <v/>
+      </c>
+      <c r="AD24" s="35">
+        <f>IF(T24=0,"",AC24/T24)</f>
+        <v/>
+      </c>
+      <c r="AE24" s="36">
+        <f>IF(AC24&lt;=0,"",VLOOKUP(B24,country_opex,7,FALSE)/AC24)</f>
+        <v/>
+      </c>
+      <c r="AF24" s="33">
+        <f>((D24*O24/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D24*O24*VLOOKUP(B24,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG24" s="31" t="n">
+        <v>296000</v>
+      </c>
+      <c r="AH24" s="32" t="n"/>
+      <c r="AI24" s="32" t="n"/>
+      <c r="AJ24" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK24" s="34">
+        <f>IF(AG24="","",AG24*AJ24)</f>
+        <v/>
+      </c>
+      <c r="AL24" s="34">
+        <f>IF(OR(AG24="",R24=0),"",MIN(IF(AT24="",9.9E+99,AT24),FLOOR(AK24/R24,1)))</f>
+        <v/>
+      </c>
+      <c r="AM24" s="38">
+        <f>IF(AL24="","",AL24*T24)</f>
+        <v/>
+      </c>
+      <c r="AN24" s="36">
+        <f>IF(OR(AG24="",R24=0),"",MIN(IF(AT24="",9.9E+99,AT24),AK24/R24))</f>
+        <v/>
+      </c>
+      <c r="AO24" s="38">
+        <f>IF(AN24="","",AN24*T24)</f>
+        <v/>
+      </c>
+      <c r="AP24" s="40" t="n"/>
+      <c r="AQ24" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AR24" s="41" t="n"/>
+      <c r="AS24" s="41" t="n"/>
+      <c r="AT24" s="42" t="n"/>
+      <c r="AU24" s="43">
+        <f>IF(((S24*pax_cap*load_thin*ROUND(K24*L24*revleg_thin,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_thin,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24))&lt;=0,"",VLOOKUP(B24,country_opex,7,FALSE)/((S24*pax_cap*load_thin*ROUND(K24*L24*revleg_thin,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_thin,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24)))</f>
+        <v/>
+      </c>
+      <c r="AV24" s="43">
+        <f>IF(((S24*pax_cap*load_mid*ROUND(K24*L24*revleg_mid,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_mid,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24))&lt;=0,"",VLOOKUP(B24,country_opex,7,FALSE)/((S24*pax_cap*load_mid*ROUND(K24*L24*revleg_mid,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_mid,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24)))</f>
+        <v/>
+      </c>
+      <c r="AW24" s="43">
+        <f>IF(((S24*pax_cap*load_full*ROUND(K24*L24*revleg_full,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_full,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24))&lt;=0,"",VLOOKUP(B24,country_opex,7,FALSE)/((S24*pax_cap*load_full*ROUND(K24*L24*revleg_full,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_full,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24)))</f>
+        <v/>
+      </c>
+      <c r="AX24" s="44" t="n"/>
+      <c r="AY24" s="44" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>Yassir</t>
+        </is>
+      </c>
+      <c r="B25" s="29" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="C25" s="30" t="inlineStr">
+        <is>
+          <t>Tunis (La Goulette) → La Marsa / Gammarth</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" s="26" t="n"/>
+      <c r="F25" s="32" t="n"/>
+      <c r="G25" s="32" t="n"/>
+      <c r="H25" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="33">
+        <f>60*D25/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J25" s="33">
+        <f>I25+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K25" s="34">
+        <f>MIN(24,FLOOR(60*service_hr/J25,1))</f>
+        <v/>
+      </c>
+      <c r="L25" s="34">
+        <f>ROUND(365*mech_uptime*H25,0)</f>
+        <v/>
+      </c>
+      <c r="M25" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N25" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O25" s="34">
+        <f>ROUND(K25*L25*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P25" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q25" s="36">
+        <f>pax_cap*P25</f>
+        <v/>
+      </c>
+      <c r="R25" s="34">
+        <f>Q25*O25</f>
+        <v/>
+      </c>
+      <c r="S25" s="37">
+        <f>E25*discount</f>
+        <v/>
+      </c>
+      <c r="T25" s="38">
+        <f>S25*R25</f>
+        <v/>
+      </c>
+      <c r="U25" s="38">
+        <f>(battery/range_nm)*D25*O25*VLOOKUP(B25,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V25" s="38">
+        <f>VLOOKUP(B25,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W25" s="38">
+        <f>VLOOKUP(B25,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X25" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y25" s="38">
+        <f>VLOOKUP(B25,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z25" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA25" s="38">
+        <f>U25+V25+W25+X25+Y25+Z25</f>
+        <v/>
+      </c>
+      <c r="AB25" s="38">
+        <f>VLOOKUP(B25,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC25" s="38">
+        <f>T25-AA25</f>
+        <v/>
+      </c>
+      <c r="AD25" s="35">
+        <f>IF(T25=0,"",AC25/T25)</f>
+        <v/>
+      </c>
+      <c r="AE25" s="36">
+        <f>IF(AC25&lt;=0,"",VLOOKUP(B25,country_opex,7,FALSE)/AC25)</f>
+        <v/>
+      </c>
+      <c r="AF25" s="33">
+        <f>((D25*O25/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D25*O25*VLOOKUP(B25,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG25" s="31" t="n">
+        <v>222000</v>
+      </c>
+      <c r="AH25" s="32" t="n"/>
+      <c r="AI25" s="32" t="n"/>
+      <c r="AJ25" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK25" s="34">
+        <f>IF(AG25="","",AG25*AJ25)</f>
+        <v/>
+      </c>
+      <c r="AL25" s="34">
+        <f>IF(OR(AG25="",R25=0),"",MIN(IF(AT25="",9.9E+99,AT25),FLOOR(AK25/R25,1)))</f>
+        <v/>
+      </c>
+      <c r="AM25" s="38">
+        <f>IF(AL25="","",AL25*T25)</f>
+        <v/>
+      </c>
+      <c r="AN25" s="36">
+        <f>IF(OR(AG25="",R25=0),"",MIN(IF(AT25="",9.9E+99,AT25),AK25/R25))</f>
+        <v/>
+      </c>
+      <c r="AO25" s="38">
+        <f>IF(AN25="","",AN25*T25)</f>
+        <v/>
+      </c>
+      <c r="AP25" s="40" t="n"/>
+      <c r="AQ25" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AR25" s="41" t="n"/>
+      <c r="AS25" s="41" t="n"/>
+      <c r="AT25" s="42" t="n"/>
+      <c r="AU25" s="43">
+        <f>IF(((S25*pax_cap*load_thin*ROUND(K25*L25*revleg_thin,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_thin,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25))&lt;=0,"",VLOOKUP(B25,country_opex,7,FALSE)/((S25*pax_cap*load_thin*ROUND(K25*L25*revleg_thin,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_thin,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25)))</f>
+        <v/>
+      </c>
+      <c r="AV25" s="43">
+        <f>IF(((S25*pax_cap*load_mid*ROUND(K25*L25*revleg_mid,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_mid,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25))&lt;=0,"",VLOOKUP(B25,country_opex,7,FALSE)/((S25*pax_cap*load_mid*ROUND(K25*L25*revleg_mid,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_mid,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25)))</f>
+        <v/>
+      </c>
+      <c r="AW25" s="43">
+        <f>IF(((S25*pax_cap*load_full*ROUND(K25*L25*revleg_full,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_full,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25))&lt;=0,"",VLOOKUP(B25,country_opex,7,FALSE)/((S25*pax_cap*load_full*ROUND(K25*L25*revleg_full,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_full,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25)))</f>
+        <v/>
+      </c>
+      <c r="AX25" s="44" t="n"/>
+      <c r="AY25" s="44" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>Yassir</t>
+        </is>
+      </c>
+      <c r="B26" s="29" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="C26" s="30" t="inlineStr">
+        <is>
+          <t>Sfax → Sidi Youssef (Kerkennah Islands)</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="E26" s="26" t="n"/>
+      <c r="F26" s="32" t="n"/>
+      <c r="G26" s="32" t="n"/>
+      <c r="H26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="33">
+        <f>60*D26/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J26" s="33">
+        <f>I26+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K26" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J26,1))</f>
+        <v/>
+      </c>
+      <c r="L26" s="34">
+        <f>ROUND(365*mech_uptime*H26,0)</f>
+        <v/>
+      </c>
+      <c r="M26" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N26" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O26" s="34">
+        <f>ROUND(K26*L26*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P26" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q26" s="36">
+        <f>pax_cap*P26</f>
+        <v/>
+      </c>
+      <c r="R26" s="34">
+        <f>Q26*O26</f>
+        <v/>
+      </c>
+      <c r="S26" s="37">
+        <f>E26*discount</f>
+        <v/>
+      </c>
+      <c r="T26" s="38">
+        <f>S26*R26</f>
+        <v/>
+      </c>
+      <c r="U26" s="38">
+        <f>(battery/range_nm)*D26*O26*VLOOKUP(B26,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V26" s="38">
+        <f>VLOOKUP(B26,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W26" s="38">
+        <f>VLOOKUP(B26,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X26" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y26" s="38">
+        <f>VLOOKUP(B26,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z26" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA26" s="38">
+        <f>U26+V26+W26+X26+Y26+Z26</f>
+        <v/>
+      </c>
+      <c r="AB26" s="38">
+        <f>VLOOKUP(B26,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC26" s="38">
+        <f>T26-AA26</f>
+        <v/>
+      </c>
+      <c r="AD26" s="35">
+        <f>IF(T26=0,"",AC26/T26)</f>
+        <v/>
+      </c>
+      <c r="AE26" s="36">
+        <f>IF(AC26&lt;=0,"",VLOOKUP(B26,country_opex,7,FALSE)/AC26)</f>
+        <v/>
+      </c>
+      <c r="AF26" s="33">
+        <f>((D26*O26/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D26*O26*VLOOKUP(B26,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG26" s="31" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="AH26" s="32" t="n"/>
+      <c r="AI26" s="32" t="n"/>
+      <c r="AJ26" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK26" s="34">
+        <f>IF(AG26="","",AG26*AJ26)</f>
+        <v/>
+      </c>
+      <c r="AL26" s="34">
+        <f>IF(OR(AG26="",R26=0),"",MIN(IF(AT26="",9.9E+99,AT26),FLOOR(AK26/R26,1)))</f>
+        <v/>
+      </c>
+      <c r="AM26" s="38">
+        <f>IF(AL26="","",AL26*T26)</f>
+        <v/>
+      </c>
+      <c r="AN26" s="36">
+        <f>IF(OR(AG26="",R26=0),"",MIN(IF(AT26="",9.9E+99,AT26),AK26/R26))</f>
+        <v/>
+      </c>
+      <c r="AO26" s="38">
+        <f>IF(AN26="","",AN26*T26)</f>
+        <v/>
+      </c>
+      <c r="AP26" s="40" t="n"/>
+      <c r="AQ26" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AR26" s="41" t="n"/>
+      <c r="AS26" s="41" t="n"/>
+      <c r="AT26" s="42" t="n"/>
+      <c r="AU26" s="43">
+        <f>IF(((S26*pax_cap*load_thin*ROUND(K26*L26*revleg_thin,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_thin,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26))&lt;=0,"",VLOOKUP(B26,country_opex,7,FALSE)/((S26*pax_cap*load_thin*ROUND(K26*L26*revleg_thin,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_thin,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26)))</f>
+        <v/>
+      </c>
+      <c r="AV26" s="43">
+        <f>IF(((S26*pax_cap*load_mid*ROUND(K26*L26*revleg_mid,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_mid,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26))&lt;=0,"",VLOOKUP(B26,country_opex,7,FALSE)/((S26*pax_cap*load_mid*ROUND(K26*L26*revleg_mid,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_mid,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26)))</f>
+        <v/>
+      </c>
+      <c r="AW26" s="43">
+        <f>IF(((S26*pax_cap*load_full*ROUND(K26*L26*revleg_full,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_full,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26))&lt;=0,"",VLOOKUP(B26,country_opex,7,FALSE)/((S26*pax_cap*load_full*ROUND(K26*L26*revleg_full,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_full,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26)))</f>
+        <v/>
+      </c>
+      <c r="AX26" s="44" t="n"/>
+      <c r="AY26" s="44" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>Yassir</t>
+        </is>
+      </c>
+      <c r="B27" s="29" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="C27" s="30" t="inlineStr">
+        <is>
+          <t>Sousse (Port El Kantaoui) → Monastir (Marina)</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="F27" s="32" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G27" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="33">
+        <f>60*D27/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J27" s="33">
+        <f>I27+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K27" s="34">
+        <f>MIN(24,FLOOR(60*service_hr/J27,1))</f>
+        <v/>
+      </c>
+      <c r="L27" s="34">
+        <f>ROUND(365*mech_uptime*H27,0)</f>
+        <v/>
+      </c>
+      <c r="M27" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N27" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O27" s="34">
+        <f>ROUND(K27*L27*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P27" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q27" s="36">
+        <f>pax_cap*P27</f>
+        <v/>
+      </c>
+      <c r="R27" s="34">
+        <f>Q27*O27</f>
+        <v/>
+      </c>
+      <c r="S27" s="37">
+        <f>E27*discount</f>
+        <v/>
+      </c>
+      <c r="T27" s="38">
+        <f>S27*R27</f>
+        <v/>
+      </c>
+      <c r="U27" s="38">
+        <f>(battery/range_nm)*D27*O27*VLOOKUP(B27,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V27" s="38">
+        <f>VLOOKUP(B27,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W27" s="38">
+        <f>VLOOKUP(B27,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X27" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y27" s="38">
+        <f>VLOOKUP(B27,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z27" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA27" s="38">
+        <f>U27+V27+W27+X27+Y27+Z27</f>
+        <v/>
+      </c>
+      <c r="AB27" s="38">
+        <f>VLOOKUP(B27,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC27" s="38">
+        <f>T27-AA27</f>
+        <v/>
+      </c>
+      <c r="AD27" s="35">
+        <f>IF(T27=0,"",AC27/T27)</f>
+        <v/>
+      </c>
+      <c r="AE27" s="36">
+        <f>IF(AC27&lt;=0,"",VLOOKUP(B27,country_opex,7,FALSE)/AC27)</f>
+        <v/>
+      </c>
+      <c r="AF27" s="33">
+        <f>((D27*O27/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D27*O27*VLOOKUP(B27,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG27" s="31" t="n">
+        <v>344000</v>
+      </c>
+      <c r="AH27" s="32" t="n"/>
+      <c r="AI27" s="32" t="n"/>
+      <c r="AJ27" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK27" s="34">
+        <f>IF(AG27="","",AG27*AJ27)</f>
+        <v/>
+      </c>
+      <c r="AL27" s="34">
+        <f>IF(OR(AG27="",R27=0),"",MIN(IF(AT27="",9.9E+99,AT27),FLOOR(AK27/R27,1)))</f>
+        <v/>
+      </c>
+      <c r="AM27" s="38">
+        <f>IF(AL27="","",AL27*T27)</f>
+        <v/>
+      </c>
+      <c r="AN27" s="36">
+        <f>IF(OR(AG27="",R27=0),"",MIN(IF(AT27="",9.9E+99,AT27),AK27/R27))</f>
+        <v/>
+      </c>
+      <c r="AO27" s="38">
+        <f>IF(AN27="","",AN27*T27)</f>
+        <v/>
+      </c>
+      <c r="AP27" s="40" t="n"/>
+      <c r="AQ27" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AR27" s="41" t="n"/>
+      <c r="AS27" s="41" t="n"/>
+      <c r="AT27" s="42" t="n"/>
+      <c r="AU27" s="43">
+        <f>IF(((S27*pax_cap*load_thin*ROUND(K27*L27*revleg_thin,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_thin,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27))&lt;=0,"",VLOOKUP(B27,country_opex,7,FALSE)/((S27*pax_cap*load_thin*ROUND(K27*L27*revleg_thin,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_thin,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27)))</f>
+        <v/>
+      </c>
+      <c r="AV27" s="43">
+        <f>IF(((S27*pax_cap*load_mid*ROUND(K27*L27*revleg_mid,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_mid,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27))&lt;=0,"",VLOOKUP(B27,country_opex,7,FALSE)/((S27*pax_cap*load_mid*ROUND(K27*L27*revleg_mid,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_mid,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27)))</f>
+        <v/>
+      </c>
+      <c r="AW27" s="43">
+        <f>IF(((S27*pax_cap*load_full*ROUND(K27*L27*revleg_full,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_full,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27))&lt;=0,"",VLOOKUP(B27,country_opex,7,FALSE)/((S27*pax_cap*load_full*ROUND(K27*L27*revleg_full,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_full,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27)))</f>
+        <v/>
+      </c>
+      <c r="AX27" s="44" t="inlineStr">
         <is>
           <t>PREMIUM charter-divided tier: Port El Kantaoui per-seat catamaran / 'pirate boat' coastal cruise ~EUR 25-35 (Catamaran Amira day-cruise; half-day pirate-boat Sousse-Monastir) -&gt; midpoint ~EUR 30 x 1.08 ~= $32. This is the nearest premium per-seat water product operating on this exact coast.</t>
         </is>
       </c>
-      <c r="AY20" s="44" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="45" t="inlineStr">
-        <is>
-          <t>TOTAL / median</t>
-        </is>
-      </c>
-      <c r="T21" s="46">
-        <f>SUM(T4:T20)</f>
-        <v/>
-      </c>
-      <c r="AC21" s="46">
-        <f>SUM(AC4:AC20)</f>
-        <v/>
-      </c>
-      <c r="AD21" s="47">
-        <f>IF(T21=0,"",AC21/T21)</f>
-        <v/>
-      </c>
-      <c r="AL21" s="48">
-        <f>SUM(AL4:AL20)</f>
-        <v/>
-      </c>
-      <c r="AM21" s="46">
-        <f>SUM(AM4:AM20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Market fleet build-up — grounded floor (network-sum of raw vessel fractions per market, rounded once; subset slices excluded; legacy per-corridor-floor totals above kept for reference)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="24" t="inlineStr">
-        <is>
-          <t>Market</t>
-        </is>
-      </c>
-      <c r="B24" s="24" t="inlineStr">
-        <is>
-          <t>Fleet basis</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>Raw vessels (sum)</t>
-        </is>
-      </c>
-      <c r="D24" s="24" t="inlineStr">
-        <is>
-          <t>Fleet (rounded once)</t>
-        </is>
-      </c>
-      <c r="E24" s="24" t="inlineStr">
-        <is>
-          <t>Market rev/yr (raw sum)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>Yassir Algeria</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>aspirational</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D25" s="49">
-        <f>SUMIFS(AL4:AL20,A4:A20,"Yassir Algeria",AP4:AP20,"=",AQ4:AQ20,"Grounded")</f>
-        <v/>
-      </c>
-      <c r="E25" s="50">
-        <f>SUMIFS(AM4:AM20,A4:A20,"Yassir Algeria",AP4:AP20,"=",AQ4:AQ20,"Grounded")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="25" t="inlineStr">
-        <is>
-          <t>Yassir Morocco</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>aspirational</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D26" s="49">
-        <f>SUMIFS(AL4:AL20,A4:A20,"Yassir Morocco",AP4:AP20,"=",AQ4:AQ20,"Grounded")</f>
-        <v/>
-      </c>
-      <c r="E26" s="50">
-        <f>SUMIFS(AM4:AM20,A4:A20,"Yassir Morocco",AP4:AP20,"=",AQ4:AQ20,"Grounded")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="25" t="inlineStr">
-        <is>
-          <t>Yassir Tunisia</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>aspirational</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" s="49">
-        <f>SUMIFS(AL4:AL20,A4:A20,"Yassir Tunisia",AP4:AP20,"=",AQ4:AQ20,"Grounded")</f>
-        <v/>
-      </c>
-      <c r="E27" s="50">
-        <f>SUMIFS(AM4:AM20,A4:A20,"Yassir Tunisia",AP4:AP20,"=",AQ4:AQ20,"Grounded")</f>
-        <v/>
-      </c>
+      <c r="AY27" s="44" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="45" t="inlineStr">
         <is>
+          <t>TOTAL / median</t>
+        </is>
+      </c>
+      <c r="T28" s="46">
+        <f>SUM(T4:T27)</f>
+        <v/>
+      </c>
+      <c r="AC28" s="46">
+        <f>SUM(AC4:AC27)</f>
+        <v/>
+      </c>
+      <c r="AD28" s="47">
+        <f>IF(T28=0,"",AC28/T28)</f>
+        <v/>
+      </c>
+      <c r="AL28" s="48">
+        <f>SUM(AL4:AL27)</f>
+        <v/>
+      </c>
+      <c r="AM28" s="46">
+        <f>SUM(AM4:AM27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Market fleet build-up — grounded floor (network-sum of raw vessel fractions per market, rounded once; subset slices excluded; legacy per-corridor-floor totals above kept for reference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>Fleet basis</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>Raw vessels (sum)</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>Fleet (rounded once)</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>Market rev/yr (raw sum)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Yassir</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>network_sum / ceil</t>
+        </is>
+      </c>
+      <c r="C32" s="23">
+        <f>SUMIFS(AN4:AN27,A4:A27,"Yassir",AP4:AP27,"=",AQ4:AQ27,"Grounded")</f>
+        <v/>
+      </c>
+      <c r="D32" s="49">
+        <f>IF(C32=0,0,CEILING(C32,1))</f>
+        <v/>
+      </c>
+      <c r="E32" s="50">
+        <f>SUMIFS(AO4:AO27,A4:A27,"Yassir",AP4:AP27,"=",AQ4:AQ27,"Grounded")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="45" t="inlineStr">
+        <is>
           <t>GROUNDED FLOOR (PUBLISHED)</t>
         </is>
       </c>
-      <c r="D28" s="48">
-        <f>SUM(D25:D27)</f>
-        <v/>
-      </c>
-      <c r="E28" s="46">
-        <f>SUM(E25:E27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="D33" s="48">
+        <f>SUM(D32:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="46">
+        <f>SUM(E32:E32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>ESTIMATED DEMAND (country-median cascade; held OUT of grounded floor)</t>
         </is>
       </c>
-      <c r="D29" s="51">
-        <f>SUMIF(AQ4:AQ20,"Estimated",AL4:AL20)</f>
-        <v/>
-      </c>
-      <c r="E29" s="52">
-        <f>SUMIF(AQ4:AQ20,"Estimated",AM4:AM20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="53" t="inlineStr">
+      <c r="D34" s="51">
+        <f>SUMIF(AQ4:AQ27,"Estimated",AL4:AL27)</f>
+        <v/>
+      </c>
+      <c r="E34" s="52">
+        <f>SUMIF(AQ4:AQ27,"Estimated",AM4:AM27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="53" t="inlineStr">
         <is>
           <t>Held for Quanta-LR (&gt;70nm, roadmap H2 2026+):</t>
         </is>
       </c>
-      <c r="C30" s="54" t="inlineStr">
+      <c r="C35" s="54" t="inlineStr">
         <is>
           <t>Tunis (La Goulette) → Palermo (Sicily, Italy) (170nm)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="C31" s="54" t="inlineStr">
+    <row r="36">
+      <c r="C36" s="54" t="inlineStr">
         <is>
           <t>Nador (Beni Ensar) → Almeria (Spain) (92nm)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="C32" s="54" t="inlineStr">
+    <row r="37">
+      <c r="C37" s="54" t="inlineStr">
         <is>
           <t>Port d'Oran → Mostaganem port (81.7nm)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="C33" s="54" t="inlineStr">
+    <row r="38">
+      <c r="C38" s="54" t="inlineStr">
         <is>
           <t>Port de Béjaïa → Port d'Alger (113.8nm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" s="54" t="inlineStr">
+        <is>
+          <t>Dakar → Saint-Louis (du Senegal) (90nm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" s="54" t="inlineStr">
+        <is>
+          <t>Dakar (Gare maritime / Port) → Ziguinchor (Port de Ziguinchor, Casamance) (200nm)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A23:L23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5703,7 +6911,7 @@
         </is>
       </c>
       <c r="C11" s="39" t="n">
-        <v>0.0922</v>
+        <v>0.0929</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
